--- a/pdks_eylul_gunluk_calisma_saatleri.xlsx
+++ b/pdks_eylul_gunluk_calisma_saatleri.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eylul_2026_Saatler" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_2026_Saatler" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -603,7 +603,7 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>01.09
-Salı</t>
+Sal</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1869,44 +1869,44 @@
       </c>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="9" t="n"/>
-      <c r="J17" s="8" t="n">
-        <v>7.5</v>
+      <c r="J17" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="N17" s="6" t="n"/>
       <c r="O17" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="6" t="n"/>
       <c r="R17" s="6" t="n"/>
-      <c r="S17" s="8" t="n">
-        <v>7.5</v>
+      <c r="S17" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="T17" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="V17" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="W17" s="9" t="n"/>
       <c r="X17" s="6" t="n"/>
@@ -1923,7 +1923,7 @@
         <v>11</v>
       </c>
       <c r="AI17" s="11" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -2722,57 +2722,57 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I29" s="9" t="n"/>
-      <c r="J29" s="8" t="n">
-        <v>6</v>
+      <c r="J29" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S29" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S29" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U29" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="V29" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="W29" s="9" t="n"/>
       <c r="X29" s="6" t="n"/>
@@ -2789,7 +2789,7 @@
         <v>17</v>
       </c>
       <c r="AI29" s="11" t="n">
-        <v>138</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -2983,50 +2983,50 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="14" t="n"/>
       <c r="H32" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I32" s="9" t="n"/>
-      <c r="J32" s="8" t="n">
-        <v>6.5</v>
+      <c r="J32" s="7" t="n">
+        <v>8.5</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="N32" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="P32" s="9" t="n"/>
       <c r="Q32" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R32" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S32" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="V32" s="14" t="n"/>
       <c r="W32" s="9" t="n"/>
@@ -3044,7 +3044,7 @@
         <v>14</v>
       </c>
       <c r="AI32" s="11" t="n">
-        <v>108</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -5379,42 +5379,42 @@
       <c r="G63" s="6" t="n"/>
       <c r="H63" s="6" t="n"/>
       <c r="I63" s="9" t="n"/>
-      <c r="J63" s="8" t="n">
-        <v>6.5</v>
+      <c r="J63" s="7" t="n">
+        <v>8.5</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="P63" s="9" t="n"/>
       <c r="Q63" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="R63" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S63" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S63" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T63" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U63" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="V63" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="W63" s="9" t="n"/>
       <c r="X63" s="6" t="n"/>
@@ -5431,7 +5431,7 @@
         <v>12</v>
       </c>
       <c r="AI63" s="11" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -7254,57 +7254,57 @@
         </is>
       </c>
       <c r="D87" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I87" s="9" t="n"/>
-      <c r="J87" s="8" t="n">
-        <v>6</v>
+      <c r="J87" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P87" s="9" t="n"/>
       <c r="Q87" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="R87" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S87" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T87" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U87" s="8" t="n">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S87" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T87" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U87" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="V87" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="W87" s="9" t="n"/>
       <c r="X87" s="6" t="n"/>
@@ -7321,7 +7321,7 @@
         <v>17</v>
       </c>
       <c r="AI87" s="11" t="n">
-        <v>138</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -8380,57 +8380,57 @@
         </is>
       </c>
       <c r="D101" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I101" s="9" t="n"/>
-      <c r="J101" s="8" t="n">
-        <v>6.5</v>
+      <c r="J101" s="7" t="n">
+        <v>8.5</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="P101" s="9" t="n"/>
       <c r="Q101" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="R101" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S101" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T101" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U101" s="8" t="n">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S101" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T101" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U101" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="V101" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="W101" s="9" t="n"/>
       <c r="X101" s="6" t="n"/>
@@ -8447,7 +8447,7 @@
         <v>17</v>
       </c>
       <c r="AI101" s="11" t="n">
-        <v>138</v>
+        <v>172</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
@@ -8626,25 +8626,25 @@
           <t>BALIK KESİM</t>
         </is>
       </c>
-      <c r="D104" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E104" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F104" s="8" t="n">
-        <v>7.5</v>
+      <c r="D104" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="G104" s="14" t="n"/>
       <c r="H104" s="14" t="n"/>
       <c r="I104" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J104" s="7" t="n">
         <v>13.5</v>
       </c>
-      <c r="K104" s="8" t="n">
-        <v>7.5</v>
+      <c r="K104" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="L104" s="7" t="n">
         <v>14</v>
@@ -8665,14 +8665,14 @@
       <c r="R104" s="7" t="n">
         <v>17.5</v>
       </c>
-      <c r="S104" s="8" t="n">
-        <v>7.5</v>
+      <c r="S104" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="T104" s="14" t="n"/>
       <c r="U104" s="14" t="n"/>
       <c r="V104" s="14" t="n"/>
-      <c r="W104" s="8" t="n">
-        <v>7</v>
+      <c r="W104" s="7" t="n">
+        <v>9</v>
       </c>
       <c r="X104" s="14" t="n"/>
       <c r="Y104" s="14" t="n"/>
@@ -8688,7 +8688,7 @@
         <v>14</v>
       </c>
       <c r="AI104" s="11" t="n">
-        <v>151.5</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -9133,7 +9133,7 @@
         <v>14.5</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="F111" s="7" t="n">
         <v>13.5</v>
@@ -9142,14 +9142,14 @@
         <v>13</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="I111" s="9" t="n"/>
-      <c r="J111" s="8" t="n">
-        <v>7</v>
+      <c r="J111" s="7" t="n">
+        <v>9</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="L111" s="7" t="n">
         <v>12.5</v>
@@ -9162,26 +9162,26 @@
         <v>14.5</v>
       </c>
       <c r="P111" s="9" t="n"/>
-      <c r="Q111" s="8" t="n">
-        <v>7.5</v>
+      <c r="Q111" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="R111" s="7" t="n">
         <v>12.5</v>
       </c>
       <c r="S111" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T111" s="7" t="n">
         <v>12</v>
       </c>
       <c r="U111" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V111" s="8" t="n">
-        <v>7.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="V111" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="W111" s="8" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="X111" s="6" t="n"/>
       <c r="Y111" s="6" t="n"/>
@@ -9197,7 +9197,7 @@
         <v>17</v>
       </c>
       <c r="AI111" s="11" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
     </row>
     <row r="112" ht="19" customHeight="1">
@@ -9604,57 +9604,57 @@
         </is>
       </c>
       <c r="D117" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I117" s="9" t="n"/>
-      <c r="J117" s="8" t="n">
-        <v>6</v>
+      <c r="J117" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K117" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L117" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M117" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="N117" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P117" s="9" t="n"/>
       <c r="Q117" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="R117" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S117" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T117" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U117" s="8" t="n">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S117" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T117" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U117" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="V117" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="W117" s="9" t="n"/>
       <c r="X117" s="6" t="n"/>
@@ -9671,7 +9671,7 @@
         <v>17</v>
       </c>
       <c r="AI117" s="11" t="n">
-        <v>138</v>
+        <v>172</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -10241,37 +10241,37 @@
           <t>BALIK KESİM</t>
         </is>
       </c>
-      <c r="D125" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F125" s="8" t="n">
-        <v>7.5</v>
+      <c r="D125" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="G125" s="7" t="n">
         <v>12.5</v>
       </c>
       <c r="H125" s="6" t="n"/>
       <c r="I125" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J125" s="6" t="n"/>
-      <c r="K125" s="8" t="n">
-        <v>7.5</v>
+      <c r="K125" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="L125" s="6" t="n"/>
       <c r="M125" s="7" t="n">
         <v>13.5</v>
       </c>
-      <c r="N125" s="8" t="n">
-        <v>7.5</v>
+      <c r="N125" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="O125" s="6" t="n"/>
       <c r="P125" s="9" t="n"/>
-      <c r="Q125" s="8" t="n">
-        <v>7.5</v>
+      <c r="Q125" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="R125" s="6" t="n"/>
       <c r="S125" s="6" t="n"/>
@@ -10293,7 +10293,7 @@
         <v>9</v>
       </c>
       <c r="AI125" s="11" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="126" ht="19" customHeight="1">
@@ -19952,51 +19952,51 @@
         </is>
       </c>
       <c r="D251" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="E251" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F251" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="G251" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H251" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I251" s="9" t="n"/>
-      <c r="J251" s="8" t="n">
-        <v>6</v>
+      <c r="J251" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K251" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L251" s="6" t="n"/>
       <c r="M251" s="6" t="n"/>
       <c r="N251" s="6" t="n"/>
       <c r="O251" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P251" s="9" t="n"/>
       <c r="Q251" s="7" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="R251" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S251" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="T251" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="U251" s="8" t="n">
-        <v>7.5</v>
+        <v>10</v>
+      </c>
+      <c r="S251" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T251" s="7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U251" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="V251" s="7" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="W251" s="9" t="n"/>
       <c r="X251" s="6" t="n"/>
@@ -20013,7 +20013,7 @@
         <v>14</v>
       </c>
       <c r="AI251" s="11" t="n">
-        <v>112.5</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="252" ht="19" customHeight="1">

--- a/pdks_eylul_gunluk_calisma_saatleri.xlsx
+++ b/pdks_eylul_gunluk_calisma_saatleri.xlsx
@@ -885,9 +885,7 @@
       <c r="D4" s="14" t="n"/>
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="14" t="n"/>
-      <c r="G4" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="G4" s="14" t="n"/>
       <c r="H4" s="8" t="n">
         <v>7.5</v>
       </c>
@@ -919,10 +917,10 @@
       <c r="AF4" s="14" t="n"/>
       <c r="AG4" s="14" t="n"/>
       <c r="AH4" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" s="11" t="n">
-        <v>25.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
@@ -945,8 +943,8 @@
       <c r="E5" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>7.5</v>
+      <c r="F5" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>8</v>
@@ -1009,7 +1007,7 @@
       </c>
       <c r="AD5" s="9" t="n"/>
       <c r="AE5" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF5" s="6" t="n"/>
       <c r="AG5" s="8" t="n">
@@ -1019,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="AI5" s="11" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -1081,7 +1079,7 @@
         <v>8.5</v>
       </c>
       <c r="V6" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W6" s="9" t="n"/>
       <c r="X6" s="14" t="n"/>
@@ -1098,7 +1096,7 @@
         <v>14</v>
       </c>
       <c r="AI6" s="11" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
@@ -1189,13 +1187,13 @@
         <v>10.5</v>
       </c>
       <c r="AC7" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AD7" s="7" t="n">
         <v>8.5</v>
       </c>
       <c r="AE7" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AF7" s="7" t="n">
         <v>9</v>
@@ -1207,7 +1205,7 @@
         <v>29</v>
       </c>
       <c r="AI7" s="11" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1247,10 +1245,10 @@
         <v>7.5</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P8" s="8" t="n">
         <v>7.5</v>
@@ -1304,7 +1302,7 @@
         <v>23</v>
       </c>
       <c r="AI8" s="11" t="n">
-        <v>183.5</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1395,84 +1393,84 @@
       <c r="D10" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>8</v>
+      <c r="E10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="I10" s="9" t="n"/>
-      <c r="J10" s="7" t="n">
-        <v>8</v>
+      <c r="J10" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="K10" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="L10" s="14" t="n"/>
-      <c r="M10" s="7" t="n">
-        <v>8</v>
+      <c r="M10" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="N10" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="O10" s="14" t="n"/>
       <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="S10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="U10" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="V10" s="7" t="n">
-        <v>8.5</v>
+      <c r="Q10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="W10" s="9" t="n"/>
-      <c r="X10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y10" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Z10" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA10" s="7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AB10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC10" s="7" t="n">
-        <v>8.5</v>
+      <c r="X10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC10" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="7" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AF10" s="7" t="n">
-        <v>8.5</v>
+      <c r="AE10" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AF10" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="AG10" s="14" t="n"/>
       <c r="AH10" s="10" t="n">
         <v>23</v>
       </c>
       <c r="AI10" s="11" t="n">
-        <v>189</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
@@ -1584,9 +1582,7 @@
       <c r="G12" s="7" t="n">
         <v>10.5</v>
       </c>
-      <c r="H12" s="7" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="H12" s="14" t="n"/>
       <c r="I12" s="9" t="n"/>
       <c r="J12" s="7" t="n">
         <v>10.5</v>
@@ -1641,10 +1637,10 @@
         <v>7.5</v>
       </c>
       <c r="AH12" s="10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI12" s="11" t="n">
-        <v>177.5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
@@ -1684,7 +1680,7 @@
         <v>7.5</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M13" s="8" t="n">
         <v>7.5</v>
@@ -1700,7 +1696,7 @@
         <v>7.5</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="S13" s="8" t="n">
         <v>7.5</v>
@@ -1713,7 +1709,7 @@
       </c>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="8" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>7.5</v>
@@ -1745,7 +1741,7 @@
         <v>25</v>
       </c>
       <c r="AI13" s="11" t="n">
-        <v>191.5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1781,7 +1777,7 @@
       <c r="L14" s="14" t="n"/>
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O14" s="7" t="n">
         <v>9.5</v>
@@ -1828,7 +1824,7 @@
         <v>16</v>
       </c>
       <c r="AI14" s="11" t="n">
-        <v>127.5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1963,7 +1959,7 @@
         <v>7.5</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O16" s="7" t="n">
         <v>9.5</v>
@@ -2000,8 +1996,8 @@
       <c r="AA16" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB16" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB16" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC16" s="8" t="n">
         <v>7.5</v>
@@ -2020,7 +2016,7 @@
         <v>24</v>
       </c>
       <c r="AI16" s="11" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -2041,14 +2037,14 @@
       <c r="E17" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>7.5</v>
+      <c r="F17" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="8" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>8.5</v>
@@ -2089,8 +2085,8 @@
       <c r="AA17" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB17" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB17" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC17" s="8" t="n">
         <v>7.5</v>
@@ -2107,7 +2103,7 @@
         <v>18</v>
       </c>
       <c r="AI17" s="11" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -2130,8 +2126,8 @@
       <c r="E18" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>7.5</v>
+      <c r="F18" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>8</v>
@@ -2149,15 +2145,13 @@
         <v>7.5</v>
       </c>
       <c r="N18" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>9.5</v>
       </c>
       <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="7" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="Q18" s="14" t="n"/>
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="8" t="n">
         <v>7.5</v>
@@ -2172,8 +2166,8 @@
         <v>8.5</v>
       </c>
       <c r="W18" s="9" t="n"/>
-      <c r="X18" s="8" t="n">
-        <v>7.5</v>
+      <c r="X18" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="Y18" s="8" t="n">
         <v>7.5</v>
@@ -2184,12 +2178,8 @@
       <c r="AA18" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB18" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AC18" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="AB18" s="14" t="n"/>
+      <c r="AC18" s="14" t="n"/>
       <c r="AD18" s="9" t="n"/>
       <c r="AE18" s="7" t="n">
         <v>8.5</v>
@@ -2201,10 +2191,10 @@
         <v>7.5</v>
       </c>
       <c r="AH18" s="10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI18" s="11" t="n">
-        <v>182</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -2281,9 +2271,11 @@
       <c r="L20" s="14" t="n"/>
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O20" s="14" t="n"/>
+        <v>10.5</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>10.5</v>
+      </c>
       <c r="P20" s="9" t="n"/>
       <c r="Q20" s="7" t="n">
         <v>10.5</v>
@@ -2329,10 +2321,10 @@
       </c>
       <c r="AG20" s="14" t="n"/>
       <c r="AH20" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI20" s="11" t="n">
-        <v>139</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -2354,13 +2346,13 @@
       </c>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G21" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H21" s="7" t="n">
         <v>14.5</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>15</v>
       </c>
       <c r="I21" s="9" t="n"/>
       <c r="J21" s="8" t="n">
@@ -2369,11 +2361,11 @@
       <c r="K21" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L21" s="8" t="n">
-        <v>0.5</v>
+      <c r="L21" s="7" t="n">
+        <v>14</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="N21" s="6" t="n"/>
       <c r="O21" s="7" t="n">
@@ -2382,7 +2374,7 @@
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="6" t="n"/>
       <c r="R21" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="S21" s="8" t="n">
         <v>7.5</v>
@@ -2391,7 +2383,7 @@
         <v>8.5</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="V21" s="7" t="n">
         <v>9.5</v>
@@ -2427,7 +2419,7 @@
         <v>22</v>
       </c>
       <c r="AI21" s="11" t="n">
-        <v>202.5</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -2450,8 +2442,8 @@
       <c r="E22" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>7.5</v>
+      <c r="F22" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>8</v>
@@ -2473,7 +2465,7 @@
         <v>7.5</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O22" s="7" t="n">
         <v>9.5</v>
@@ -2518,10 +2510,10 @@
       </c>
       <c r="AD22" s="9" t="n"/>
       <c r="AE22" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF22" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF22" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG22" s="8" t="n">
         <v>7.5</v>
@@ -2530,7 +2522,7 @@
         <v>26</v>
       </c>
       <c r="AI22" s="11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -2701,8 +2693,8 @@
       <c r="E25" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>7.5</v>
+      <c r="F25" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G25" s="6" t="n"/>
       <c r="H25" s="6" t="n"/>
@@ -2735,7 +2727,7 @@
         <v>3</v>
       </c>
       <c r="AI25" s="11" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -2796,7 +2788,7 @@
         <v>9.5</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="T26" s="8" t="n">
         <v>7</v>
@@ -2838,7 +2830,7 @@
         <v>26</v>
       </c>
       <c r="AI26" s="11" t="n">
-        <v>208.5</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -2877,8 +2869,8 @@
       <c r="K27" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <v>7.5</v>
+      <c r="L27" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M27" s="8" t="n">
         <v>7.5</v>
@@ -2923,7 +2915,7 @@
         <v>17</v>
       </c>
       <c r="AI27" s="11" t="n">
-        <v>134</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -3043,7 +3035,7 @@
         <v>6</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L29" s="7" t="n">
         <v>8</v>
@@ -3087,10 +3079,10 @@
         <v>9</v>
       </c>
       <c r="AA29" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AC29" s="8" t="n">
         <v>7</v>
@@ -3107,7 +3099,7 @@
         <v>25</v>
       </c>
       <c r="AI29" s="11" t="n">
-        <v>197</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -3141,56 +3133,58 @@
       </c>
       <c r="I30" s="9" t="n"/>
       <c r="J30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N30" s="7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R30" s="8" t="n">
         <v>4</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U30" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="V30" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W30" s="9" t="n"/>
+        <v>10.5</v>
+      </c>
+      <c r="W30" s="7" t="n">
+        <v>10.5</v>
+      </c>
       <c r="X30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA30" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB30" s="14" t="n"/>
       <c r="AC30" s="14" t="n"/>
@@ -3199,10 +3193,10 @@
       <c r="AF30" s="14" t="n"/>
       <c r="AG30" s="14" t="n"/>
       <c r="AH30" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI30" s="11" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
@@ -3231,12 +3225,12 @@
       <c r="G31" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H31" s="8" t="n">
-        <v>7.5</v>
+      <c r="H31" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="I31" s="9" t="n"/>
-      <c r="J31" s="8" t="n">
-        <v>7.5</v>
+      <c r="J31" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K31" s="8" t="n">
         <v>7.5</v>
@@ -3307,7 +3301,7 @@
         <v>27</v>
       </c>
       <c r="AI31" s="11" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
@@ -3340,7 +3334,7 @@
         <v>6.5</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L32" s="7" t="n">
         <v>8</v>
@@ -3361,9 +3355,7 @@
       <c r="R32" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="S32" s="8" t="n">
-        <v>6</v>
-      </c>
+      <c r="S32" s="14" t="n"/>
       <c r="T32" s="8" t="n">
         <v>6.5</v>
       </c>
@@ -3379,10 +3371,10 @@
         <v>7</v>
       </c>
       <c r="Z32" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA32" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB32" s="8" t="n">
         <v>7</v>
@@ -3397,10 +3389,10 @@
       <c r="AF32" s="14" t="n"/>
       <c r="AG32" s="14" t="n"/>
       <c r="AH32" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI32" s="11" t="n">
-        <v>159.5</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -3421,7 +3413,7 @@
         <v>8.5</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>9.5</v>
@@ -3443,7 +3435,7 @@
         <v>5</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N33" s="7" t="n">
         <v>11.5</v>
@@ -3452,8 +3444,8 @@
         <v>6.5</v>
       </c>
       <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="8" t="n">
-        <v>7.5</v>
+      <c r="Q33" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="R33" s="7" t="n">
         <v>12.5</v>
@@ -3472,7 +3464,7 @@
         <v>7.5</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA33" s="7" t="n">
         <v>8</v>
@@ -3487,8 +3479,8 @@
       <c r="AE33" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="AF33" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF33" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG33" s="8" t="n">
         <v>7.5</v>
@@ -3497,7 +3489,7 @@
         <v>23</v>
       </c>
       <c r="AI33" s="11" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
@@ -3518,8 +3510,8 @@
         <v>7.5</v>
       </c>
       <c r="E34" s="14" t="n"/>
-      <c r="F34" s="8" t="n">
-        <v>7.5</v>
+      <c r="F34" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>8</v>
@@ -3539,7 +3531,7 @@
         <v>7.5</v>
       </c>
       <c r="N34" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O34" s="7" t="n">
         <v>9.5</v>
@@ -3582,8 +3574,8 @@
       <c r="AE34" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="AF34" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF34" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG34" s="8" t="n">
         <v>7.5</v>
@@ -3592,7 +3584,7 @@
         <v>22</v>
       </c>
       <c r="AI34" s="11" t="n">
-        <v>171.5</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
@@ -3615,16 +3607,16 @@
       <c r="G35" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H35" s="8" t="n">
-        <v>7.5</v>
+      <c r="H35" s="7" t="n">
+        <v>14.5</v>
       </c>
       <c r="I35" s="9" t="n"/>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M35" s="6" t="n"/>
       <c r="N35" s="6" t="n"/>
@@ -3651,7 +3643,7 @@
         <v>4</v>
       </c>
       <c r="AI35" s="11" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
@@ -3688,8 +3680,8 @@
         <v>7.5</v>
       </c>
       <c r="K36" s="14" t="n"/>
-      <c r="L36" s="8" t="n">
-        <v>7.5</v>
+      <c r="L36" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M36" s="14" t="n"/>
       <c r="N36" s="7" t="n">
@@ -3713,7 +3705,7 @@
         <v>8.5</v>
       </c>
       <c r="V36" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W36" s="9" t="n"/>
       <c r="X36" s="8" t="n">
@@ -3732,7 +3724,7 @@
       </c>
       <c r="AD36" s="9" t="n"/>
       <c r="AE36" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF36" s="7" t="n">
         <v>8</v>
@@ -3744,7 +3736,7 @@
         <v>21</v>
       </c>
       <c r="AI36" s="11" t="n">
-        <v>165.5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
@@ -3790,13 +3782,11 @@
       <c r="N37" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="O37" s="8" t="n">
-        <v>7.5</v>
+      <c r="O37" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="7" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="Q37" s="6" t="n"/>
       <c r="R37" s="8" t="n">
         <v>7.5</v>
       </c>
@@ -3820,8 +3810,8 @@
       <c r="Z37" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA37" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA37" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB37" s="8" t="n">
         <v>7.5</v>
@@ -3831,19 +3821,19 @@
       </c>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF37" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF37" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG37" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AH37" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI37" s="11" t="n">
-        <v>186</v>
+        <v>179.5</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
@@ -3891,8 +3881,8 @@
       <c r="N38" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="O38" s="8" t="n">
-        <v>7.5</v>
+      <c r="O38" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="P38" s="8" t="n">
         <v>7.5</v>
@@ -3909,7 +3899,7 @@
         <v>8.5</v>
       </c>
       <c r="V38" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W38" s="9" t="n"/>
       <c r="X38" s="8" t="n">
@@ -3940,7 +3930,7 @@
         <v>23</v>
       </c>
       <c r="AI38" s="11" t="n">
-        <v>189.5</v>
+        <v>190.5</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -4082,7 +4072,7 @@
       </c>
       <c r="I41" s="9" t="n"/>
       <c r="J41" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="K41" s="6" t="n"/>
       <c r="L41" s="6" t="n"/>
@@ -4111,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="AI41" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
@@ -4153,7 +4143,7 @@
         <v>7.5</v>
       </c>
       <c r="N42" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O42" s="7" t="n">
         <v>9.5</v>
@@ -4206,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="AI42" s="11" t="n">
-        <v>174.5</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
@@ -4346,7 +4336,7 @@
         <v>7.5</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L44" s="7" t="n">
         <v>9.5</v>
@@ -4364,7 +4354,7 @@
         <v>7</v>
       </c>
       <c r="Q44" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R44" s="7" t="n">
         <v>9.5</v>
@@ -4376,7 +4366,7 @@
         <v>8.5</v>
       </c>
       <c r="U44" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="V44" s="7" t="n">
         <v>10.5</v>
@@ -4418,7 +4408,7 @@
         <v>29</v>
       </c>
       <c r="AI44" s="11" t="n">
-        <v>251</v>
+        <v>252.5</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -4447,8 +4437,8 @@
       <c r="K45" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L45" s="8" t="n">
-        <v>7.5</v>
+      <c r="L45" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M45" s="8" t="n">
         <v>7.5</v>
@@ -4457,7 +4447,7 @@
         <v>7.5</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="7" t="n">
@@ -4474,7 +4464,7 @@
         <v>8.5</v>
       </c>
       <c r="V45" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W45" s="9" t="n"/>
       <c r="X45" s="6" t="n"/>
@@ -4507,7 +4497,7 @@
         <v>19</v>
       </c>
       <c r="AI45" s="11" t="n">
-        <v>149</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -4573,7 +4563,7 @@
         <v>8.5</v>
       </c>
       <c r="V46" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W46" s="9" t="n"/>
       <c r="X46" s="8" t="n">
@@ -4606,7 +4596,7 @@
         <v>24</v>
       </c>
       <c r="AI46" s="11" t="n">
-        <v>187.5</v>
+        <v>186.5</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
@@ -4652,7 +4642,7 @@
         <v>7.5</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O47" s="7" t="n">
         <v>9.5</v>
@@ -4683,8 +4673,8 @@
         <v>7.5</v>
       </c>
       <c r="AA47" s="6" t="n"/>
-      <c r="AB47" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB47" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC47" s="8" t="n">
         <v>7.5</v>
@@ -4703,7 +4693,7 @@
         <v>23</v>
       </c>
       <c r="AI47" s="11" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
@@ -4739,11 +4729,11 @@
       <c r="J48" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="K48" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="L48" s="8" t="n">
-        <v>7.5</v>
+      <c r="K48" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M48" s="8" t="n">
         <v>7.5</v>
@@ -4783,9 +4773,7 @@
       <c r="Z48" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA48" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="AA48" s="14" t="n"/>
       <c r="AB48" s="8" t="n">
         <v>7.5</v>
       </c>
@@ -4805,10 +4793,10 @@
         <v>7.5</v>
       </c>
       <c r="AH48" s="10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI48" s="11" t="n">
-        <v>220.5</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
@@ -4831,8 +4819,8 @@
       <c r="E49" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F49" s="8" t="n">
-        <v>7.5</v>
+      <c r="F49" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>8</v>
@@ -4852,7 +4840,7 @@
         <v>7.5</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O49" s="7" t="n">
         <v>9.5</v>
@@ -4909,7 +4897,7 @@
         <v>25</v>
       </c>
       <c r="AI49" s="11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
@@ -5165,8 +5153,8 @@
       <c r="E53" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F53" s="8" t="n">
-        <v>7.5</v>
+      <c r="F53" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>8</v>
@@ -5233,7 +5221,7 @@
         <v>20</v>
       </c>
       <c r="AI53" s="11" t="n">
-        <v>162.5</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
@@ -5335,9 +5323,7 @@
       <c r="K55" s="7" t="n">
         <v>10.5</v>
       </c>
-      <c r="L55" s="7" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="L55" s="6" t="n"/>
       <c r="M55" s="7" t="n">
         <v>10.5</v>
       </c>
@@ -5394,10 +5380,10 @@
         <v>7.5</v>
       </c>
       <c r="AH55" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI55" s="11" t="n">
-        <v>207</v>
+        <v>196.5</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
@@ -5450,7 +5436,7 @@
         <v>8.5</v>
       </c>
       <c r="Q56" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R56" s="14" t="n"/>
       <c r="S56" s="14" t="n"/>
@@ -5467,11 +5453,9 @@
       <c r="X56" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="Y56" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z56" s="8" t="n">
-        <v>7.5</v>
+      <c r="Y56" s="14" t="n"/>
+      <c r="Z56" s="7" t="n">
+        <v>15.5</v>
       </c>
       <c r="AA56" s="8" t="n">
         <v>7.5</v>
@@ -5482,21 +5466,21 @@
       <c r="AC56" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AD56" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE56" s="8" t="n">
-        <v>7.5</v>
+      <c r="AD56" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE56" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AF56" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AG56" s="14" t="n"/>
       <c r="AH56" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI56" s="11" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -5545,7 +5529,7 @@
       </c>
       <c r="P57" s="9" t="n"/>
       <c r="Q57" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R57" s="8" t="n">
         <v>7.5</v>
@@ -5572,18 +5556,18 @@
       <c r="Z57" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA57" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AB57" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA57" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB57" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC57" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AD57" s="9" t="n"/>
       <c r="AE57" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF57" s="7" t="n">
         <v>8.5</v>
@@ -5595,7 +5579,7 @@
         <v>24</v>
       </c>
       <c r="AI57" s="11" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
@@ -5618,8 +5602,8 @@
       <c r="E58" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F58" s="8" t="n">
-        <v>7.5</v>
+      <c r="F58" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>8</v>
@@ -5628,9 +5612,7 @@
         <v>8</v>
       </c>
       <c r="I58" s="9" t="n"/>
-      <c r="J58" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="J58" s="14" t="n"/>
       <c r="K58" s="7" t="n">
         <v>8.5</v>
       </c>
@@ -5666,8 +5648,8 @@
         <v>8.5</v>
       </c>
       <c r="W58" s="9" t="n"/>
-      <c r="X58" s="8" t="n">
-        <v>7.5</v>
+      <c r="X58" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="Y58" s="8" t="n">
         <v>7.5</v>
@@ -5676,10 +5658,10 @@
         <v>7.5</v>
       </c>
       <c r="AA58" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB58" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AC58" s="7" t="n">
         <v>8.5</v>
@@ -5695,10 +5677,10 @@
         <v>7.5</v>
       </c>
       <c r="AH58" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI58" s="11" t="n">
-        <v>209.5</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
@@ -5770,8 +5752,8 @@
       <c r="Z59" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA59" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA59" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB59" s="8" t="n">
         <v>7.5</v>
@@ -5779,10 +5761,10 @@
       <c r="AC59" s="6" t="n"/>
       <c r="AD59" s="9" t="n"/>
       <c r="AE59" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF59" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF59" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG59" s="8" t="n">
         <v>7.5</v>
@@ -5791,7 +5773,7 @@
         <v>21</v>
       </c>
       <c r="AI59" s="11" t="n">
-        <v>165</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
@@ -5809,46 +5791,46 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O60" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="M60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O60" s="7" t="n">
-        <v>12</v>
-      </c>
       <c r="P60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R60" s="7" t="n">
         <v>9.5</v>
@@ -5857,50 +5839,50 @@
         <v>9.5</v>
       </c>
       <c r="T60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="X60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y60" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AB60" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC60" s="7" t="n">
         <v>11.5</v>
       </c>
-      <c r="U60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="V60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="W60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="X60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y60" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB60" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC60" s="7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AD60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF60" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG60" s="14" t="n"/>
       <c r="AH60" s="10" t="n">
         <v>29</v>
       </c>
       <c r="AI60" s="11" t="n">
-        <v>322.5</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -5929,8 +5911,8 @@
       <c r="G61" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H61" s="8" t="n">
-        <v>7.5</v>
+      <c r="H61" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="I61" s="9" t="n"/>
       <c r="J61" s="8" t="n">
@@ -6001,7 +5983,7 @@
         <v>25</v>
       </c>
       <c r="AI61" s="11" t="n">
-        <v>201.5</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
@@ -6019,94 +6001,94 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="I62" s="9" t="n"/>
       <c r="J62" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M62" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N62" s="7" t="n">
         <v>11.5</v>
       </c>
-      <c r="K62" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L62" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M62" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N62" s="7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="O62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R62" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="S62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="V62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W62" s="9" t="n"/>
       <c r="X62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB62" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AC62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF62" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG62" s="14" t="n"/>
       <c r="AH62" s="10" t="n">
         <v>27</v>
       </c>
       <c r="AI62" s="11" t="n">
-        <v>303.5</v>
+        <v>278.5</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
@@ -6133,7 +6115,7 @@
         <v>6.5</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L63" s="7" t="n">
         <v>8</v>
@@ -6174,10 +6156,10 @@
         <v>7</v>
       </c>
       <c r="Z63" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA63" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB63" s="8" t="n">
         <v>7</v>
@@ -6197,7 +6179,7 @@
         <v>20</v>
       </c>
       <c r="AI63" s="11" t="n">
-        <v>153.5</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -6232,7 +6214,7 @@
         <v>7.5</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L64" s="14" t="n"/>
       <c r="M64" s="7" t="n">
@@ -6290,7 +6272,7 @@
         <v>21</v>
       </c>
       <c r="AI64" s="11" t="n">
-        <v>158.5</v>
+        <v>158</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
@@ -6350,7 +6332,7 @@
         <v>7.5</v>
       </c>
       <c r="T65" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="U65" s="8" t="n">
         <v>7</v>
@@ -6391,7 +6373,7 @@
         <v>25</v>
       </c>
       <c r="AI65" s="11" t="n">
-        <v>196.5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
@@ -6503,7 +6485,7 @@
         <v>9.5</v>
       </c>
       <c r="S67" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="T67" s="8" t="n">
         <v>7.5</v>
@@ -6535,7 +6517,7 @@
         <v>20</v>
       </c>
       <c r="AI67" s="11" t="n">
-        <v>165.5</v>
+        <v>166</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
@@ -6564,12 +6546,12 @@
       <c r="G68" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H68" s="8" t="n">
-        <v>7.5</v>
+      <c r="H68" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="I68" s="9" t="n"/>
-      <c r="J68" s="8" t="n">
-        <v>7.5</v>
+      <c r="J68" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K68" s="8" t="n">
         <v>7.5</v>
@@ -6638,7 +6620,7 @@
         <v>26</v>
       </c>
       <c r="AI68" s="11" t="n">
-        <v>209.5</v>
+        <v>210.5</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
@@ -6904,7 +6886,7 @@
         <v>5</v>
       </c>
       <c r="X71" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Y71" s="7" t="n">
         <v>9</v>
@@ -6935,7 +6917,7 @@
         <v>29</v>
       </c>
       <c r="AI71" s="11" t="n">
-        <v>244.5</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
@@ -6958,8 +6940,8 @@
       <c r="E72" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F72" s="8" t="n">
-        <v>7.5</v>
+      <c r="F72" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>8</v>
@@ -7026,8 +7008,8 @@
       <c r="AE72" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="AF72" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF72" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG72" s="8" t="n">
         <v>7.5</v>
@@ -7036,7 +7018,7 @@
         <v>25</v>
       </c>
       <c r="AI72" s="11" t="n">
-        <v>199.5</v>
+        <v>200.5</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
@@ -7071,8 +7053,8 @@
       <c r="K73" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L73" s="8" t="n">
-        <v>7.5</v>
+      <c r="L73" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M73" s="8" t="n">
         <v>7.5</v>
@@ -7085,7 +7067,7 @@
       </c>
       <c r="P73" s="9" t="n"/>
       <c r="Q73" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R73" s="8" t="n">
         <v>7.5</v>
@@ -7100,7 +7082,7 @@
         <v>8.5</v>
       </c>
       <c r="V73" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W73" s="9" t="n"/>
       <c r="X73" s="6" t="n"/>
@@ -7123,8 +7105,8 @@
       <c r="AE73" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AF73" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF73" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG73" s="8" t="n">
         <v>7.5</v>
@@ -7133,7 +7115,7 @@
         <v>23</v>
       </c>
       <c r="AI73" s="11" t="n">
-        <v>179.5</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
@@ -7156,8 +7138,8 @@
       <c r="E74" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F74" s="8" t="n">
-        <v>7.5</v>
+      <c r="F74" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>8</v>
@@ -7173,7 +7155,7 @@
         <v>7.5</v>
       </c>
       <c r="N74" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O74" s="7" t="n">
         <v>9.5</v>
@@ -7210,8 +7192,8 @@
       <c r="AA74" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB74" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB74" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC74" s="14" t="n"/>
       <c r="AD74" s="9" t="n"/>
@@ -7228,7 +7210,7 @@
         <v>22</v>
       </c>
       <c r="AI74" s="11" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
@@ -7251,8 +7233,8 @@
       <c r="E75" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F75" s="8" t="n">
-        <v>7.5</v>
+      <c r="F75" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>8</v>
@@ -7274,7 +7256,7 @@
         <v>7.5</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O75" s="7" t="n">
         <v>9.5</v>
@@ -7319,7 +7301,7 @@
       </c>
       <c r="AD75" s="9" t="n"/>
       <c r="AE75" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF75" s="7" t="n">
         <v>8</v>
@@ -7331,7 +7313,7 @@
         <v>26</v>
       </c>
       <c r="AI75" s="11" t="n">
-        <v>206.5</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
@@ -7352,7 +7334,7 @@
         <v>7.5</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="F76" s="8" t="n">
         <v>7.5</v>
@@ -7385,10 +7367,10 @@
         <v>8</v>
       </c>
       <c r="P76" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q76" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="Q76" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="R76" s="7" t="n">
         <v>10.5</v>
@@ -7403,7 +7385,7 @@
         <v>10.5</v>
       </c>
       <c r="V76" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W76" s="9" t="n"/>
       <c r="X76" s="8" t="n">
@@ -7440,7 +7422,7 @@
         <v>29</v>
       </c>
       <c r="AI76" s="11" t="n">
-        <v>259.5</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
@@ -7467,8 +7449,8 @@
       <c r="K77" s="7" t="n">
         <v>10.5</v>
       </c>
-      <c r="L77" s="8" t="n">
-        <v>7.5</v>
+      <c r="L77" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M77" s="6" t="n"/>
       <c r="N77" s="7" t="n">
@@ -7511,7 +7493,7 @@
         <v>10</v>
       </c>
       <c r="AI77" s="11" t="n">
-        <v>88</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
@@ -7718,8 +7700,8 @@
         <v>7.5</v>
       </c>
       <c r="E80" s="14" t="n"/>
-      <c r="F80" s="8" t="n">
-        <v>7.5</v>
+      <c r="F80" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>8</v>
@@ -7762,8 +7744,8 @@
         <v>8.5</v>
       </c>
       <c r="W80" s="9" t="n"/>
-      <c r="X80" s="8" t="n">
-        <v>7.5</v>
+      <c r="X80" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="Y80" s="8" t="n">
         <v>7.5</v>
@@ -7784,7 +7766,7 @@
         <v>18</v>
       </c>
       <c r="AI80" s="11" t="n">
-        <v>143.5</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
@@ -7851,9 +7833,7 @@
       <c r="U81" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="V81" s="7" t="n">
-        <v>14</v>
-      </c>
+      <c r="V81" s="6" t="n"/>
       <c r="W81" s="9" t="n"/>
       <c r="X81" s="8" t="n">
         <v>7.5</v>
@@ -7875,19 +7855,19 @@
       </c>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF81" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF81" s="8" t="n">
+        <v>6.5</v>
       </c>
       <c r="AG81" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AH81" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI81" s="11" t="n">
-        <v>218.5</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -7925,18 +7905,18 @@
       </c>
       <c r="K82" s="14" t="n"/>
       <c r="L82" s="14" t="n"/>
-      <c r="M82" s="7" t="n">
-        <v>18.5</v>
+      <c r="M82" s="8" t="n">
+        <v>6.5</v>
       </c>
       <c r="N82" s="7" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="O82" s="7" t="n">
         <v>10.5</v>
       </c>
       <c r="P82" s="9" t="n"/>
-      <c r="Q82" s="7" t="n">
-        <v>10.5</v>
+      <c r="Q82" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="R82" s="14" t="n"/>
       <c r="S82" s="14" t="n"/>
@@ -7958,7 +7938,7 @@
         <v>10</v>
       </c>
       <c r="AI82" s="11" t="n">
-        <v>97.5</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
@@ -8095,76 +8075,76 @@
       <c r="J84" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="K84" s="8" t="n">
-        <v>7.5</v>
+      <c r="K84" s="7" t="n">
+        <v>10.5</v>
       </c>
       <c r="L84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q84" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="R84" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T84" s="7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="U84" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V84" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="W84" s="9" t="n"/>
       <c r="X84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y84" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="Z84" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA84" s="7" t="n">
-        <v>10.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="AA84" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="AB84" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC84" s="7" t="n">
-        <v>10.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="AC84" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="AD84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF84" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG84" s="14" t="n"/>
       <c r="AH84" s="10" t="n">
         <v>27</v>
       </c>
       <c r="AI84" s="11" t="n">
-        <v>266.5</v>
+        <v>249.5</v>
       </c>
     </row>
     <row r="85" ht="19" customHeight="1">
@@ -8245,9 +8225,7 @@
       <c r="D86" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="E86" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="E86" s="14" t="n"/>
       <c r="F86" s="14" t="n"/>
       <c r="G86" s="8" t="n">
         <v>7.5</v>
@@ -8281,10 +8259,10 @@
       <c r="AF86" s="14" t="n"/>
       <c r="AG86" s="14" t="n"/>
       <c r="AH86" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI86" s="11" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
@@ -8321,7 +8299,7 @@
         <v>6</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L87" s="7" t="n">
         <v>8</v>
@@ -8337,7 +8315,7 @@
       </c>
       <c r="P87" s="9" t="n"/>
       <c r="Q87" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R87" s="7" t="n">
         <v>8</v>
@@ -8365,7 +8343,7 @@
         <v>9</v>
       </c>
       <c r="AA87" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB87" s="8" t="n">
         <v>7</v>
@@ -8385,7 +8363,7 @@
         <v>25</v>
       </c>
       <c r="AI87" s="11" t="n">
-        <v>197.5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -8453,7 +8431,7 @@
         <v>8.5</v>
       </c>
       <c r="V88" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W88" s="9" t="n"/>
       <c r="X88" s="8" t="n">
@@ -8482,7 +8460,7 @@
         <v>23</v>
       </c>
       <c r="AI88" s="11" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -8562,8 +8540,8 @@
       <c r="Z89" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA89" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA89" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB89" s="8" t="n">
         <v>7.5</v>
@@ -8575,8 +8553,8 @@
       <c r="AE89" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AF89" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF89" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG89" s="8" t="n">
         <v>7.5</v>
@@ -8585,7 +8563,7 @@
         <v>26</v>
       </c>
       <c r="AI89" s="11" t="n">
-        <v>204.5</v>
+        <v>205.5</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
@@ -8655,7 +8633,7 @@
         <v>8.5</v>
       </c>
       <c r="V90" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W90" s="9" t="n"/>
       <c r="X90" s="14" t="n"/>
@@ -8678,7 +8656,7 @@
         <v>21</v>
       </c>
       <c r="AI90" s="11" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="91" ht="19" customHeight="1">
@@ -8746,7 +8724,7 @@
         <v>8.5</v>
       </c>
       <c r="V91" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W91" s="9" t="n"/>
       <c r="X91" s="8" t="n">
@@ -8779,7 +8757,7 @@
         <v>25</v>
       </c>
       <c r="AI91" s="11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
@@ -8897,8 +8875,8 @@
       <c r="K93" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L93" s="8" t="n">
-        <v>7.5</v>
+      <c r="L93" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M93" s="8" t="n">
         <v>7.5</v>
@@ -8936,8 +8914,8 @@
       <c r="Z93" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA93" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA93" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB93" s="8" t="n">
         <v>7.5</v>
@@ -8947,10 +8925,10 @@
       </c>
       <c r="AD93" s="9" t="n"/>
       <c r="AE93" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF93" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF93" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG93" s="8" t="n">
         <v>7.5</v>
@@ -8959,7 +8937,7 @@
         <v>23</v>
       </c>
       <c r="AI93" s="11" t="n">
-        <v>181.5</v>
+        <v>183.5</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
@@ -8992,8 +8970,8 @@
       <c r="U94" s="14" t="n"/>
       <c r="V94" s="14" t="n"/>
       <c r="W94" s="9" t="n"/>
-      <c r="X94" s="7" t="n">
-        <v>8</v>
+      <c r="X94" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="Y94" s="14" t="n"/>
       <c r="Z94" s="14" t="n"/>
@@ -9008,7 +8986,7 @@
         <v>1</v>
       </c>
       <c r="AI94" s="11" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
@@ -9138,8 +9116,8 @@
       <c r="K96" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L96" s="8" t="n">
-        <v>7.5</v>
+      <c r="L96" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M96" s="8" t="n">
         <v>7.5</v>
@@ -9173,17 +9151,17 @@
       <c r="Z96" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA96" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA96" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB96" s="14" t="n"/>
       <c r="AC96" s="14" t="n"/>
       <c r="AD96" s="9" t="n"/>
       <c r="AE96" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF96" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF96" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG96" s="8" t="n">
         <v>7.5</v>
@@ -9192,7 +9170,7 @@
         <v>19</v>
       </c>
       <c r="AI96" s="11" t="n">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
@@ -9316,8 +9294,8 @@
       <c r="E98" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F98" s="8" t="n">
-        <v>7.5</v>
+      <c r="F98" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>8</v>
@@ -9335,7 +9313,7 @@
       <c r="L98" s="14" t="n"/>
       <c r="M98" s="14" t="n"/>
       <c r="N98" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O98" s="7" t="n">
         <v>9.5</v>
@@ -9368,7 +9346,7 @@
         <v>12</v>
       </c>
       <c r="AI98" s="11" t="n">
-        <v>95.5</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
@@ -9389,8 +9367,8 @@
       <c r="E99" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F99" s="8" t="n">
-        <v>7.5</v>
+      <c r="F99" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>8</v>
@@ -9447,7 +9425,7 @@
         <v>14</v>
       </c>
       <c r="AI99" s="11" t="n">
-        <v>111.5</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
@@ -9591,8 +9569,8 @@
       <c r="K101" s="7" t="n">
         <v>10.5</v>
       </c>
-      <c r="L101" s="8" t="n">
-        <v>7.5</v>
+      <c r="L101" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M101" s="6" t="n"/>
       <c r="N101" s="6" t="n"/>
@@ -9619,7 +9597,7 @@
         <v>8</v>
       </c>
       <c r="AI101" s="11" t="n">
-        <v>72</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
@@ -9656,7 +9634,7 @@
         <v>6.5</v>
       </c>
       <c r="K102" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L102" s="7" t="n">
         <v>8</v>
@@ -9697,10 +9675,10 @@
         <v>7</v>
       </c>
       <c r="Z102" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA102" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB102" s="8" t="n">
         <v>7</v>
@@ -9720,7 +9698,7 @@
         <v>25</v>
       </c>
       <c r="AI102" s="11" t="n">
-        <v>196.5</v>
+        <v>198</v>
       </c>
     </row>
     <row r="103" ht="19" customHeight="1">
@@ -9781,7 +9759,7 @@
         <v>9.5</v>
       </c>
       <c r="S103" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="T103" s="8" t="n">
         <v>7</v>
@@ -9825,7 +9803,7 @@
         <v>27</v>
       </c>
       <c r="AI103" s="11" t="n">
-        <v>217</v>
+        <v>217.5</v>
       </c>
     </row>
     <row r="104" ht="19" customHeight="1">
@@ -9860,8 +9838,8 @@
       <c r="K104" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L104" s="8" t="n">
-        <v>7.5</v>
+      <c r="L104" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M104" s="14" t="n"/>
       <c r="N104" s="7" t="n">
@@ -9893,8 +9871,8 @@
         <v>7.5</v>
       </c>
       <c r="Z104" s="14" t="n"/>
-      <c r="AA104" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA104" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB104" s="8" t="n">
         <v>7.5</v>
@@ -9902,8 +9880,8 @@
       <c r="AC104" s="14" t="n"/>
       <c r="AD104" s="9" t="n"/>
       <c r="AE104" s="14" t="n"/>
-      <c r="AF104" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF104" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG104" s="8" t="n">
         <v>7.5</v>
@@ -9912,7 +9890,7 @@
         <v>18</v>
       </c>
       <c r="AI104" s="11" t="n">
-        <v>141</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -9941,32 +9919,32 @@
       <c r="G105" s="6" t="n"/>
       <c r="H105" s="6" t="n"/>
       <c r="I105" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J105" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="K105" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O105" s="6" t="n"/>
       <c r="P105" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q105" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R105" s="7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="S105" s="8" t="n">
         <v>7.5</v>
@@ -10009,7 +9987,7 @@
         <v>23</v>
       </c>
       <c r="AI105" s="11" t="n">
-        <v>217.5</v>
+        <v>208.5</v>
       </c>
     </row>
     <row r="106" ht="19" customHeight="1">
@@ -10028,8 +10006,8 @@
       </c>
       <c r="D106" s="14" t="n"/>
       <c r="E106" s="14" t="n"/>
-      <c r="F106" s="8" t="n">
-        <v>7.5</v>
+      <c r="F106" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>8</v>
@@ -10084,10 +10062,10 @@
       </c>
       <c r="AD106" s="9" t="n"/>
       <c r="AE106" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF106" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF106" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG106" s="8" t="n">
         <v>7.5</v>
@@ -10096,7 +10074,7 @@
         <v>18</v>
       </c>
       <c r="AI106" s="11" t="n">
-        <v>142.5</v>
+        <v>144</v>
       </c>
     </row>
     <row r="107" ht="19" customHeight="1">
@@ -10142,7 +10120,7 @@
         <v>7.5</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O107" s="7" t="n">
         <v>9.5</v>
@@ -10176,8 +10154,8 @@
       <c r="Z107" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA107" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA107" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB107" s="8" t="n">
         <v>7.5</v>
@@ -10187,10 +10165,10 @@
       </c>
       <c r="AD107" s="9" t="n"/>
       <c r="AE107" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF107" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF107" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG107" s="8" t="n">
         <v>7.5</v>
@@ -10199,7 +10177,7 @@
         <v>26</v>
       </c>
       <c r="AI107" s="11" t="n">
-        <v>205.5</v>
+        <v>207.5</v>
       </c>
     </row>
     <row r="108" ht="19" customHeight="1">
@@ -10275,8 +10253,8 @@
       <c r="E109" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F109" s="8" t="n">
-        <v>7.5</v>
+      <c r="F109" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G109" s="7" t="n">
         <v>9.5</v>
@@ -10337,7 +10315,7 @@
         <v>17</v>
       </c>
       <c r="AI109" s="11" t="n">
-        <v>137</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
@@ -10541,8 +10519,8 @@
       <c r="Z112" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA112" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA112" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB112" s="8" t="n">
         <v>7.5</v>
@@ -10552,10 +10530,10 @@
       </c>
       <c r="AD112" s="9" t="n"/>
       <c r="AE112" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF112" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF112" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG112" s="8" t="n">
         <v>7.5</v>
@@ -10564,7 +10542,7 @@
         <v>23</v>
       </c>
       <c r="AI112" s="11" t="n">
-        <v>180.5</v>
+        <v>182</v>
       </c>
     </row>
     <row r="113" ht="19" customHeight="1">
@@ -10598,7 +10576,7 @@
       </c>
       <c r="I113" s="9" t="n"/>
       <c r="J113" s="8" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="K113" s="7" t="n">
         <v>9.5</v>
@@ -10618,7 +10596,7 @@
         <v>7.5</v>
       </c>
       <c r="R113" s="7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="S113" s="7" t="n">
         <v>9</v>
@@ -10627,7 +10605,7 @@
         <v>10</v>
       </c>
       <c r="U113" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="V113" s="8" t="n">
         <v>7.5</v>
@@ -10648,14 +10626,14 @@
         <v>7</v>
       </c>
       <c r="AB113" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AC113" s="7" t="n">
         <v>8.5</v>
       </c>
       <c r="AD113" s="9" t="n"/>
-      <c r="AE113" s="8" t="n">
-        <v>7.5</v>
+      <c r="AE113" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AF113" s="8" t="n">
         <v>6.5</v>
@@ -10667,7 +10645,7 @@
         <v>26</v>
       </c>
       <c r="AI113" s="11" t="n">
-        <v>221.5</v>
+        <v>224</v>
       </c>
     </row>
     <row r="114" ht="19" customHeight="1">
@@ -10895,7 +10873,7 @@
         <v>8.5</v>
       </c>
       <c r="V116" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W116" s="9" t="n"/>
       <c r="X116" s="8" t="n">
@@ -10928,7 +10906,7 @@
         <v>24</v>
       </c>
       <c r="AI116" s="11" t="n">
-        <v>187.5</v>
+        <v>186.5</v>
       </c>
     </row>
     <row r="117" ht="19" customHeight="1">
@@ -10972,7 +10950,7 @@
         <v>7.5</v>
       </c>
       <c r="N117" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O117" s="7" t="n">
         <v>9.5</v>
@@ -10996,7 +10974,7 @@
         <v>8.5</v>
       </c>
       <c r="V117" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W117" s="9" t="n"/>
       <c r="X117" s="8" t="n">
@@ -11033,7 +11011,7 @@
         <v>27</v>
       </c>
       <c r="AI117" s="11" t="n">
-        <v>217.5</v>
+        <v>218.5</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -11072,8 +11050,8 @@
       <c r="K118" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L118" s="8" t="n">
-        <v>7.5</v>
+      <c r="L118" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M118" s="8" t="n">
         <v>7.5</v>
@@ -11111,8 +11089,8 @@
       <c r="Z118" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA118" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA118" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB118" s="8" t="n">
         <v>7.5</v>
@@ -11124,8 +11102,8 @@
       <c r="AE118" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AF118" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF118" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG118" s="8" t="n">
         <v>7.5</v>
@@ -11134,7 +11112,7 @@
         <v>25</v>
       </c>
       <c r="AI118" s="11" t="n">
-        <v>196</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="119" ht="19" customHeight="1">
@@ -11171,7 +11149,7 @@
         <v>6</v>
       </c>
       <c r="K119" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L119" s="7" t="n">
         <v>8</v>
@@ -11187,7 +11165,7 @@
       </c>
       <c r="P119" s="9" t="n"/>
       <c r="Q119" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R119" s="7" t="n">
         <v>8</v>
@@ -11215,7 +11193,7 @@
         <v>9</v>
       </c>
       <c r="AA119" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB119" s="8" t="n">
         <v>7</v>
@@ -11235,7 +11213,7 @@
         <v>25</v>
       </c>
       <c r="AI119" s="11" t="n">
-        <v>197</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
@@ -11274,8 +11252,8 @@
       <c r="K120" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L120" s="8" t="n">
-        <v>7.5</v>
+      <c r="L120" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M120" s="8" t="n">
         <v>7.5</v>
@@ -11309,8 +11287,8 @@
       <c r="Z120" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA120" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA120" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB120" s="8" t="n">
         <v>7.5</v>
@@ -11332,7 +11310,7 @@
         <v>23</v>
       </c>
       <c r="AI120" s="11" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="121" ht="19" customHeight="1">
@@ -11362,9 +11340,7 @@
       <c r="H121" s="6" t="n"/>
       <c r="I121" s="9" t="n"/>
       <c r="J121" s="6" t="n"/>
-      <c r="K121" s="7" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="K121" s="6" t="n"/>
       <c r="L121" s="8" t="n">
         <v>7.5</v>
       </c>
@@ -11414,10 +11390,10 @@
       </c>
       <c r="AG121" s="6" t="n"/>
       <c r="AH121" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI121" s="11" t="n">
-        <v>166.5</v>
+        <v>156</v>
       </c>
     </row>
     <row r="122" ht="19" customHeight="1">
@@ -11464,7 +11440,7 @@
         <v>7.5</v>
       </c>
       <c r="O122" s="7" t="n">
-        <v>9.5</v>
+        <v>8.02</v>
       </c>
       <c r="P122" s="9" t="n"/>
       <c r="Q122" s="8" t="n">
@@ -11506,7 +11482,7 @@
         <v>19</v>
       </c>
       <c r="AI122" s="11" t="n">
-        <v>145</v>
+        <v>143.52</v>
       </c>
     </row>
     <row r="123" ht="19" customHeight="1">
@@ -11545,8 +11521,8 @@
       <c r="K123" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L123" s="8" t="n">
-        <v>7.5</v>
+      <c r="L123" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M123" s="6" t="n"/>
       <c r="N123" s="6" t="n"/>
@@ -11579,7 +11555,7 @@
         <v>11</v>
       </c>
       <c r="AI123" s="11" t="n">
-        <v>86.5</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" ht="19" customHeight="1">
@@ -11608,12 +11584,12 @@
       <c r="G124" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H124" s="8" t="n">
-        <v>7.5</v>
+      <c r="H124" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="I124" s="9" t="n"/>
-      <c r="J124" s="8" t="n">
-        <v>7.5</v>
+      <c r="J124" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K124" s="14" t="n"/>
       <c r="L124" s="8" t="n">
@@ -11672,7 +11648,7 @@
         <v>21</v>
       </c>
       <c r="AI124" s="11" t="n">
-        <v>169.5</v>
+        <v>170.5</v>
       </c>
     </row>
     <row r="125" ht="19" customHeight="1">
@@ -11701,12 +11677,12 @@
       <c r="G125" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H125" s="8" t="n">
-        <v>7.5</v>
+      <c r="H125" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="I125" s="9" t="n"/>
-      <c r="J125" s="8" t="n">
-        <v>7.5</v>
+      <c r="J125" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K125" s="8" t="n">
         <v>7.5</v>
@@ -11727,9 +11703,7 @@
       <c r="S125" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="T125" s="8" t="n">
-        <v>7</v>
-      </c>
+      <c r="T125" s="6" t="n"/>
       <c r="U125" s="7" t="n">
         <v>10</v>
       </c>
@@ -11766,10 +11740,10 @@
         <v>7.5</v>
       </c>
       <c r="AH125" s="10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI125" s="11" t="n">
-        <v>184.5</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="126" ht="19" customHeight="1">
@@ -11808,7 +11782,7 @@
         <v>10</v>
       </c>
       <c r="K126" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L126" s="7" t="n">
         <v>9.5</v>
@@ -11841,7 +11815,7 @@
         <v>8.5</v>
       </c>
       <c r="V126" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W126" s="7" t="n">
         <v>8</v>
@@ -11859,7 +11833,7 @@
         <v>10.5</v>
       </c>
       <c r="AB126" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AC126" s="8" t="n">
         <v>7.5</v>
@@ -11880,7 +11854,7 @@
         <v>30</v>
       </c>
       <c r="AI126" s="11" t="n">
-        <v>273</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="127" ht="19" customHeight="1">
@@ -11927,16 +11901,16 @@
         <v>7.5</v>
       </c>
       <c r="AA127" s="6" t="n"/>
-      <c r="AB127" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB127" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC127" s="6" t="n"/>
       <c r="AD127" s="9" t="n"/>
       <c r="AE127" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="AF127" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF127" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG127" s="8" t="n">
         <v>7.5</v>
@@ -11945,7 +11919,7 @@
         <v>7</v>
       </c>
       <c r="AI127" s="11" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="128" ht="19" customHeight="1">
@@ -11972,22 +11946,22 @@
         <v>7.5</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H128" s="14" t="n"/>
       <c r="I128" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J128" s="14" t="n"/>
       <c r="K128" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L128" s="14" t="n"/>
       <c r="M128" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N128" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O128" s="14" t="n"/>
       <c r="P128" s="9" t="n"/>
@@ -12018,7 +11992,7 @@
       </c>
       <c r="AD128" s="9" t="n"/>
       <c r="AE128" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF128" s="7" t="n">
         <v>10.5</v>
@@ -12030,7 +12004,7 @@
         <v>17</v>
       </c>
       <c r="AI128" s="11" t="n">
-        <v>154.5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="129" ht="19" customHeight="1">
@@ -12079,11 +12053,11 @@
         <v>9.5</v>
       </c>
       <c r="O129" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="P129" s="9" t="n"/>
       <c r="Q129" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R129" s="7" t="n">
         <v>10</v>
@@ -12111,8 +12085,8 @@
       <c r="AA129" s="7" t="n">
         <v>18.5</v>
       </c>
-      <c r="AB129" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB129" s="7" t="n">
+        <v>19.5</v>
       </c>
       <c r="AC129" s="7" t="n">
         <v>10.5</v>
@@ -12131,7 +12105,7 @@
         <v>25</v>
       </c>
       <c r="AI129" s="11" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="130" ht="19" customHeight="1">
@@ -12216,13 +12190,13 @@
         <v>7.5</v>
       </c>
       <c r="AC130" s="7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD130" s="8" t="n">
         <v>6</v>
       </c>
       <c r="AE130" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF130" s="7" t="n">
         <v>8</v>
@@ -12234,7 +12208,7 @@
         <v>26</v>
       </c>
       <c r="AI130" s="11" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="131" ht="19" customHeight="1">
@@ -12257,8 +12231,8 @@
       <c r="E131" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F131" s="8" t="n">
-        <v>7.5</v>
+      <c r="F131" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G131" s="6" t="n"/>
       <c r="H131" s="6" t="n"/>
@@ -12276,7 +12250,7 @@
         <v>7.5</v>
       </c>
       <c r="N131" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O131" s="7" t="n">
         <v>9.5</v>
@@ -12321,8 +12295,8 @@
       </c>
       <c r="AD131" s="9" t="n"/>
       <c r="AE131" s="6" t="n"/>
-      <c r="AF131" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF131" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG131" s="8" t="n">
         <v>7.5</v>
@@ -12331,7 +12305,7 @@
         <v>23</v>
       </c>
       <c r="AI131" s="11" t="n">
-        <v>182</v>
+        <v>183.5</v>
       </c>
     </row>
     <row r="132" ht="19" customHeight="1">
@@ -12358,8 +12332,8 @@
       <c r="G132" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H132" s="8" t="n">
-        <v>7.5</v>
+      <c r="H132" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="I132" s="9" t="n"/>
       <c r="J132" s="8" t="n">
@@ -12430,7 +12404,7 @@
         <v>24</v>
       </c>
       <c r="AI132" s="11" t="n">
-        <v>189</v>
+        <v>189.5</v>
       </c>
     </row>
     <row r="133" ht="19" customHeight="1">
@@ -12453,8 +12427,8 @@
       <c r="E133" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F133" s="8" t="n">
-        <v>7.5</v>
+      <c r="F133" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G133" s="7" t="n">
         <v>8</v>
@@ -12499,8 +12473,8 @@
         <v>8.5</v>
       </c>
       <c r="W133" s="9" t="n"/>
-      <c r="X133" s="8" t="n">
-        <v>7.5</v>
+      <c r="X133" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="Y133" s="8" t="n">
         <v>7.5</v>
@@ -12510,7 +12484,7 @@
       </c>
       <c r="AA133" s="6" t="n"/>
       <c r="AB133" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AC133" s="7" t="n">
         <v>8.5</v>
@@ -12529,7 +12503,7 @@
         <v>24</v>
       </c>
       <c r="AI133" s="11" t="n">
-        <v>193.5</v>
+        <v>195</v>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
@@ -12550,89 +12524,91 @@
         <v>5</v>
       </c>
       <c r="E134" s="7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F134" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="G134" s="8" t="n">
-        <v>2.5</v>
+      <c r="G134" s="7" t="n">
+        <v>9.5</v>
       </c>
       <c r="H134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="I134" s="9" t="n"/>
-      <c r="J134" s="14" t="n"/>
+      <c r="J134" s="7" t="n">
+        <v>10.5</v>
+      </c>
       <c r="K134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="S134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="V134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W134" s="9" t="n"/>
       <c r="X134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z134" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB134" s="7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF134" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG134" s="14" t="n"/>
       <c r="AH134" s="10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI134" s="11" t="n">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="135" ht="19" customHeight="1">
@@ -12662,11 +12638,11 @@
       <c r="J135" s="6" t="n"/>
       <c r="K135" s="6" t="n"/>
       <c r="L135" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M135" s="6" t="n"/>
       <c r="N135" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O135" s="6" t="n"/>
       <c r="P135" s="9" t="n"/>
@@ -12675,10 +12651,10 @@
         <v>4</v>
       </c>
       <c r="S135" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T135" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U135" s="8" t="n">
         <v>7.5</v>
@@ -12699,7 +12675,7 @@
         <v>8</v>
       </c>
       <c r="AI135" s="11" t="n">
-        <v>72.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="136" ht="19" customHeight="1">
@@ -12850,8 +12826,8 @@
       <c r="N137" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="O137" s="7" t="n">
-        <v>8</v>
+      <c r="O137" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="P137" s="7" t="n">
         <v>9</v>
@@ -12860,10 +12836,10 @@
         <v>9</v>
       </c>
       <c r="R137" s="8" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="S137" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="T137" s="8" t="n">
         <v>6</v>
@@ -12891,13 +12867,13 @@
         <v>8.5</v>
       </c>
       <c r="AC137" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AD137" s="7" t="n">
         <v>8.5</v>
       </c>
       <c r="AE137" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AF137" s="7" t="n">
         <v>9</v>
@@ -12907,7 +12883,7 @@
         <v>28</v>
       </c>
       <c r="AI137" s="11" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="138" ht="19" customHeight="1">
@@ -13072,11 +13048,11 @@
         <v>9.5</v>
       </c>
       <c r="O140" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="P140" s="9" t="n"/>
       <c r="Q140" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R140" s="7" t="n">
         <v>10</v>
@@ -13126,7 +13102,7 @@
         <v>27</v>
       </c>
       <c r="AI140" s="11" t="n">
-        <v>228.5</v>
+        <v>229.5</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -13154,7 +13130,7 @@
       <c r="L141" s="6" t="n"/>
       <c r="M141" s="6" t="n"/>
       <c r="N141" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O141" s="6" t="n"/>
       <c r="P141" s="9" t="n"/>
@@ -13187,8 +13163,8 @@
       <c r="AA141" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB141" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB141" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC141" s="8" t="n">
         <v>7.5</v>
@@ -13207,7 +13183,7 @@
         <v>15</v>
       </c>
       <c r="AI141" s="11" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -13225,58 +13201,58 @@
         </is>
       </c>
       <c r="D142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="E142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="F142" s="14" t="n"/>
       <c r="G142" s="14" t="n"/>
       <c r="H142" s="14" t="n"/>
       <c r="I142" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J142" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K142" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L142" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M142" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N142" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O142" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P142" s="7" t="n">
         <v>11.5</v>
       </c>
-      <c r="J142" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K142" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L142" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M142" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N142" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O142" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="P142" s="7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="Q142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="S142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="V142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="X142" s="8" t="n">
         <v>7.5</v>
@@ -13285,32 +13261,32 @@
         <v>10.5</v>
       </c>
       <c r="Z142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC142" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE142" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AF142" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG142" s="14" t="n"/>
       <c r="AH142" s="10" t="n">
         <v>26</v>
       </c>
       <c r="AI142" s="11" t="n">
-        <v>291.5</v>
+        <v>268.5</v>
       </c>
     </row>
     <row r="143" ht="19" customHeight="1">
@@ -13356,7 +13332,7 @@
         <v>7.5</v>
       </c>
       <c r="N143" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O143" s="7" t="n">
         <v>9.5</v>
@@ -13378,8 +13354,8 @@
       <c r="Z143" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA143" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA143" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB143" s="8" t="n">
         <v>7.5</v>
@@ -13395,7 +13371,7 @@
         <v>17</v>
       </c>
       <c r="AI143" s="11" t="n">
-        <v>133.5</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="144" ht="19" customHeight="1">
@@ -13418,8 +13394,8 @@
       <c r="K144" s="14" t="n"/>
       <c r="L144" s="14" t="n"/>
       <c r="M144" s="14" t="n"/>
-      <c r="N144" s="8" t="n">
-        <v>7.5</v>
+      <c r="N144" s="7" t="n">
+        <v>10.5</v>
       </c>
       <c r="O144" s="7" t="n">
         <v>10.5</v>
@@ -13470,7 +13446,7 @@
         <v>14</v>
       </c>
       <c r="AI144" s="11" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1">
@@ -13493,7 +13469,9 @@
       <c r="E145" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="F145" s="6" t="n"/>
+      <c r="F145" s="7" t="n">
+        <v>15</v>
+      </c>
       <c r="G145" s="6" t="n"/>
       <c r="H145" s="6" t="n"/>
       <c r="I145" s="9" t="n"/>
@@ -13501,10 +13479,10 @@
         <v>3.5</v>
       </c>
       <c r="K145" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L145" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M145" s="8" t="n">
         <v>7.5</v>
@@ -13525,7 +13503,7 @@
         <v>9.5</v>
       </c>
       <c r="S145" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="T145" s="8" t="n">
         <v>7.5</v>
@@ -13534,7 +13512,7 @@
         <v>12.5</v>
       </c>
       <c r="V145" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W145" s="9" t="n"/>
       <c r="X145" s="8" t="n">
@@ -13566,10 +13544,10 @@
         <v>7.5</v>
       </c>
       <c r="AH145" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI145" s="11" t="n">
-        <v>202.5</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="146" ht="19" customHeight="1">
@@ -13605,14 +13583,14 @@
       <c r="T146" s="14" t="n"/>
       <c r="U146" s="14" t="n"/>
       <c r="V146" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W146" s="9" t="n"/>
       <c r="X146" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y146" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z146" s="14" t="n"/>
       <c r="AA146" s="14" t="n"/>
@@ -13628,7 +13606,7 @@
         <v>4</v>
       </c>
       <c r="AI146" s="11" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="147" ht="19" customHeight="1">
@@ -13675,15 +13653,15 @@
       </c>
       <c r="AD147" s="9" t="n"/>
       <c r="AE147" s="6" t="n"/>
-      <c r="AF147" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF147" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG147" s="6" t="n"/>
       <c r="AH147" s="10" t="n">
         <v>2</v>
       </c>
       <c r="AI147" s="11" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -13791,8 +13769,8 @@
       <c r="K149" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L149" s="8" t="n">
-        <v>7.5</v>
+      <c r="L149" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M149" s="8" t="n">
         <v>7.5</v>
@@ -13833,10 +13811,10 @@
       <c r="AC149" s="6" t="n"/>
       <c r="AD149" s="9" t="n"/>
       <c r="AE149" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF149" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF149" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG149" s="8" t="n">
         <v>7.5</v>
@@ -13845,7 +13823,7 @@
         <v>19</v>
       </c>
       <c r="AI149" s="11" t="n">
-        <v>148.5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" ht="19" customHeight="1">
@@ -13868,8 +13846,8 @@
       <c r="K150" s="14" t="n"/>
       <c r="L150" s="14" t="n"/>
       <c r="M150" s="14" t="n"/>
-      <c r="N150" s="8" t="n">
-        <v>7.5</v>
+      <c r="N150" s="7" t="n">
+        <v>10.5</v>
       </c>
       <c r="O150" s="7" t="n">
         <v>10.5</v>
@@ -13924,7 +13902,7 @@
         <v>16</v>
       </c>
       <c r="AI150" s="11" t="n">
-        <v>157.5</v>
+        <v>160.5</v>
       </c>
     </row>
     <row r="151" ht="19" customHeight="1">
@@ -13950,45 +13928,45 @@
       </c>
       <c r="I151" s="9" t="n"/>
       <c r="J151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="K151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N151" s="6" t="n"/>
       <c r="O151" s="6" t="n"/>
       <c r="P151" s="9" t="n"/>
       <c r="Q151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R151" s="6" t="n"/>
       <c r="S151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="V151" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W151" s="9" t="n"/>
       <c r="X151" s="6" t="n"/>
       <c r="Y151" s="6" t="n"/>
       <c r="Z151" s="6" t="n"/>
       <c r="AA151" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB151" s="7" t="n">
-        <v>10.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="AB151" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="AC151" s="6" t="n"/>
       <c r="AD151" s="9" t="n"/>
@@ -13999,7 +13977,7 @@
         <v>12</v>
       </c>
       <c r="AI151" s="11" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="152" ht="19" customHeight="1">
@@ -14055,18 +14033,18 @@
       <c r="P152" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q152" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R152" s="8" t="n">
-        <v>7.5</v>
+      <c r="Q152" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R152" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="S152" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="T152" s="14" t="n"/>
-      <c r="U152" s="8" t="n">
-        <v>7.5</v>
+      <c r="U152" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="V152" s="14" t="n"/>
       <c r="W152" s="7" t="n">
@@ -14075,8 +14053,8 @@
       <c r="X152" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="Y152" s="8" t="n">
-        <v>7.5</v>
+      <c r="Y152" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="Z152" s="8" t="n">
         <v>5.5</v>
@@ -14106,7 +14084,7 @@
         <v>28</v>
       </c>
       <c r="AI152" s="11" t="n">
-        <v>217.5</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="153" ht="19" customHeight="1">
@@ -14131,21 +14109,21 @@
       <c r="I153" s="9" t="n"/>
       <c r="J153" s="6" t="n"/>
       <c r="K153" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L153" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M153" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N153" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O153" s="6" t="n"/>
       <c r="P153" s="9" t="n"/>
       <c r="Q153" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R153" s="8" t="n">
         <v>4</v>
@@ -14164,14 +14142,14 @@
       <c r="AD153" s="9" t="n"/>
       <c r="AE153" s="6" t="n"/>
       <c r="AF153" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG153" s="6" t="n"/>
       <c r="AH153" s="10" t="n">
         <v>7</v>
       </c>
       <c r="AI153" s="11" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="154" ht="19" customHeight="1">
@@ -14198,15 +14176,17 @@
         <v>7.5</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="H154" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="I154" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="J154" s="14" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="J154" s="7" t="n">
+        <v>11</v>
+      </c>
       <c r="K154" s="7" t="n">
         <v>10.5</v>
       </c>
@@ -14220,7 +14200,7 @@
         <v>7.5</v>
       </c>
       <c r="O154" s="7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="P154" s="7" t="n">
         <v>10.5</v>
@@ -14275,10 +14255,10 @@
         <v>7.5</v>
       </c>
       <c r="AH154" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI154" s="11" t="n">
-        <v>249.5</v>
+        <v>249</v>
       </c>
     </row>
     <row r="155" ht="19" customHeight="1">
@@ -14305,7 +14285,7 @@
         <v>7.5</v>
       </c>
       <c r="G155" s="7" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="H155" s="8" t="n">
         <v>7.5</v>
@@ -14315,13 +14295,11 @@
         <v>3.5</v>
       </c>
       <c r="K155" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L155" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M155" s="8" t="n">
-        <v>6</v>
+        <v>10.5</v>
+      </c>
+      <c r="L155" s="6" t="n"/>
+      <c r="M155" s="7" t="n">
+        <v>11.83</v>
       </c>
       <c r="N155" s="8" t="n">
         <v>5.5</v>
@@ -14334,13 +14312,13 @@
       </c>
       <c r="Q155" s="6" t="n"/>
       <c r="R155" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="S155" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="T155" s="7" t="n">
-        <v>9.5</v>
+      <c r="T155" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="U155" s="7" t="n">
         <v>10.5</v>
@@ -14352,13 +14330,13 @@
         <v>5.5</v>
       </c>
       <c r="X155" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y155" s="8" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
+      </c>
+      <c r="Y155" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="Z155" s="7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA155" s="7" t="n">
         <v>10.5</v>
@@ -14374,14 +14352,14 @@
         <v>10.5</v>
       </c>
       <c r="AF155" s="7" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AG155" s="6" t="n"/>
       <c r="AH155" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI155" s="11" t="n">
-        <v>218.5</v>
+        <v>211.83</v>
       </c>
     </row>
     <row r="156" ht="19" customHeight="1">
@@ -14459,8 +14437,8 @@
       <c r="Z156" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA156" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA156" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB156" s="8" t="n">
         <v>7.5</v>
@@ -14482,7 +14460,7 @@
         <v>25</v>
       </c>
       <c r="AI156" s="11" t="n">
-        <v>196.5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="157" ht="19" customHeight="1">
@@ -14519,7 +14497,7 @@
         <v>7.5</v>
       </c>
       <c r="M157" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N157" s="6" t="n"/>
       <c r="O157" s="7" t="n">
@@ -14547,7 +14525,7 @@
         <v>12.5</v>
       </c>
       <c r="W157" s="7" t="n">
-        <v>11.5</v>
+        <v>10.02</v>
       </c>
       <c r="X157" s="7" t="n">
         <v>11</v>
@@ -14559,7 +14537,7 @@
         <v>7.5</v>
       </c>
       <c r="AA157" s="7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AB157" s="7" t="n">
         <v>14</v>
@@ -14571,7 +14549,7 @@
         <v>11.5</v>
       </c>
       <c r="AE157" s="7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AF157" s="7" t="n">
         <v>11.5</v>
@@ -14583,7 +14561,7 @@
         <v>25</v>
       </c>
       <c r="AI157" s="11" t="n">
-        <v>293.5</v>
+        <v>292.02</v>
       </c>
     </row>
     <row r="158" ht="19" customHeight="1">
@@ -14672,8 +14650,8 @@
         <v>10.5</v>
       </c>
       <c r="AC158" s="14" t="n"/>
-      <c r="AD158" s="8" t="n">
-        <v>7.5</v>
+      <c r="AD158" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AE158" s="7" t="n">
         <v>10.5</v>
@@ -14688,7 +14666,7 @@
         <v>27</v>
       </c>
       <c r="AI158" s="11" t="n">
-        <v>241</v>
+        <v>241.5</v>
       </c>
     </row>
     <row r="159" ht="19" customHeight="1">
@@ -14792,8 +14770,8 @@
       <c r="E160" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F160" s="8" t="n">
-        <v>7.5</v>
+      <c r="F160" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>8</v>
@@ -14815,7 +14793,7 @@
         <v>7.5</v>
       </c>
       <c r="N160" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O160" s="7" t="n">
         <v>9.5</v>
@@ -14850,18 +14828,18 @@
       <c r="AA160" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB160" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB160" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC160" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AD160" s="9" t="n"/>
       <c r="AE160" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF160" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF160" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG160" s="8" t="n">
         <v>7.5</v>
@@ -14870,7 +14848,7 @@
         <v>25</v>
       </c>
       <c r="AI160" s="11" t="n">
-        <v>198.5</v>
+        <v>201</v>
       </c>
     </row>
     <row r="161" ht="19" customHeight="1">
@@ -14946,8 +14924,8 @@
       <c r="Z161" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA161" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA161" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB161" s="8" t="n">
         <v>7.5</v>
@@ -14957,10 +14935,10 @@
       </c>
       <c r="AD161" s="9" t="n"/>
       <c r="AE161" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF161" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF161" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG161" s="8" t="n">
         <v>7.5</v>
@@ -14969,7 +14947,7 @@
         <v>24</v>
       </c>
       <c r="AI161" s="11" t="n">
-        <v>188</v>
+        <v>189.5</v>
       </c>
     </row>
     <row r="162" ht="19" customHeight="1">
@@ -15073,8 +15051,8 @@
       <c r="E163" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F163" s="8" t="n">
-        <v>7.5</v>
+      <c r="F163" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G163" s="7" t="n">
         <v>8</v>
@@ -15095,8 +15073,8 @@
       <c r="M163" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="N163" s="8" t="n">
-        <v>7.5</v>
+      <c r="N163" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="O163" s="7" t="n">
         <v>9.5</v>
@@ -15130,8 +15108,8 @@
       <c r="Z163" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA163" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA163" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB163" s="8" t="n">
         <v>7.5</v>
@@ -15141,10 +15119,10 @@
       </c>
       <c r="AD163" s="9" t="n"/>
       <c r="AE163" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF163" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF163" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG163" s="8" t="n">
         <v>7.5</v>
@@ -15153,7 +15131,7 @@
         <v>26</v>
       </c>
       <c r="AI163" s="11" t="n">
-        <v>205</v>
+        <v>207.5</v>
       </c>
     </row>
     <row r="164" ht="19" customHeight="1">
@@ -15192,8 +15170,8 @@
       <c r="K164" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L164" s="8" t="n">
-        <v>7.5</v>
+      <c r="L164" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M164" s="8" t="n">
         <v>7.5</v>
@@ -15233,8 +15211,8 @@
       <c r="Z164" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA164" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA164" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB164" s="8" t="n">
         <v>7.5</v>
@@ -15256,7 +15234,7 @@
         <v>26</v>
       </c>
       <c r="AI164" s="11" t="n">
-        <v>204.5</v>
+        <v>205.5</v>
       </c>
     </row>
     <row r="165" ht="19" customHeight="1">
@@ -15294,8 +15272,8 @@
       <c r="J165" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="K165" s="8" t="n">
-        <v>7.5</v>
+      <c r="K165" s="7" t="n">
+        <v>7.65</v>
       </c>
       <c r="L165" s="8" t="n">
         <v>7.5</v>
@@ -15347,7 +15325,7 @@
         <v>7.5</v>
       </c>
       <c r="AC165" s="8" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AD165" s="7" t="n">
         <v>8</v>
@@ -15363,7 +15341,7 @@
         <v>28</v>
       </c>
       <c r="AI165" s="11" t="n">
-        <v>209</v>
+        <v>210.65</v>
       </c>
     </row>
     <row r="166" ht="19" customHeight="1">
@@ -15409,7 +15387,7 @@
         <v>7.5</v>
       </c>
       <c r="N166" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O166" s="7" t="n">
         <v>9.5</v>
@@ -15438,8 +15416,8 @@
       <c r="Y166" s="14" t="n"/>
       <c r="Z166" s="14" t="n"/>
       <c r="AA166" s="14" t="n"/>
-      <c r="AB166" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB166" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC166" s="8" t="n">
         <v>7.5</v>
@@ -15458,7 +15436,7 @@
         <v>22</v>
       </c>
       <c r="AI166" s="11" t="n">
-        <v>176.5</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="167" ht="19" customHeight="1">
@@ -15481,8 +15459,8 @@
       <c r="E167" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F167" s="8" t="n">
-        <v>7.5</v>
+      <c r="F167" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G167" s="7" t="n">
         <v>8</v>
@@ -15498,7 +15476,7 @@
         <v>7.5</v>
       </c>
       <c r="N167" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O167" s="7" t="n">
         <v>9.5</v>
@@ -15535,8 +15513,8 @@
       <c r="AA167" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB167" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB167" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC167" s="8" t="n">
         <v>7.5</v>
@@ -15555,7 +15533,7 @@
         <v>23</v>
       </c>
       <c r="AI167" s="11" t="n">
-        <v>183</v>
+        <v>184.5</v>
       </c>
     </row>
     <row r="168" ht="19" customHeight="1">
@@ -15578,8 +15556,8 @@
       <c r="E168" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F168" s="8" t="n">
-        <v>7.5</v>
+      <c r="F168" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>8</v>
@@ -15652,7 +15630,7 @@
         <v>23</v>
       </c>
       <c r="AI168" s="11" t="n">
-        <v>184.5</v>
+        <v>185</v>
       </c>
     </row>
     <row r="169" ht="19" customHeight="1">
@@ -15691,8 +15669,8 @@
       <c r="K169" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L169" s="8" t="n">
-        <v>7.5</v>
+      <c r="L169" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M169" s="8" t="n">
         <v>7.5</v>
@@ -15732,8 +15710,8 @@
       <c r="Z169" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA169" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA169" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB169" s="8" t="n">
         <v>7.5</v>
@@ -15743,10 +15721,10 @@
       </c>
       <c r="AD169" s="9" t="n"/>
       <c r="AE169" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF169" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF169" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG169" s="8" t="n">
         <v>7.5</v>
@@ -15755,7 +15733,7 @@
         <v>26</v>
       </c>
       <c r="AI169" s="11" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="170" ht="19" customHeight="1">
@@ -15834,8 +15812,8 @@
       <c r="Y170" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="Z170" s="8" t="n">
-        <v>7.5</v>
+      <c r="Z170" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AA170" s="8" t="n">
         <v>7.5</v>
@@ -15860,7 +15838,7 @@
         <v>27</v>
       </c>
       <c r="AI170" s="11" t="n">
-        <v>202.5</v>
+        <v>203</v>
       </c>
     </row>
     <row r="171" ht="19" customHeight="1">
@@ -15960,8 +15938,8 @@
       <c r="K172" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L172" s="8" t="n">
-        <v>7.5</v>
+      <c r="L172" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M172" s="8" t="n">
         <v>7.5</v>
@@ -16001,8 +15979,8 @@
       <c r="Z172" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA172" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA172" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB172" s="14" t="n"/>
       <c r="AC172" s="8" t="n">
@@ -16022,7 +16000,7 @@
         <v>25</v>
       </c>
       <c r="AI172" s="11" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="173" ht="19" customHeight="1">
@@ -16061,8 +16039,8 @@
       <c r="K173" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L173" s="8" t="n">
-        <v>7.5</v>
+      <c r="L173" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M173" s="8" t="n">
         <v>7.5</v>
@@ -16071,7 +16049,7 @@
         <v>7.5</v>
       </c>
       <c r="O173" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="P173" s="9" t="n"/>
       <c r="Q173" s="7" t="n">
@@ -16088,7 +16066,7 @@
         <v>8.5</v>
       </c>
       <c r="V173" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W173" s="9" t="n"/>
       <c r="X173" s="8" t="n">
@@ -16123,7 +16101,7 @@
         <v>25</v>
       </c>
       <c r="AI173" s="11" t="n">
-        <v>196</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="174" ht="19" customHeight="1">
@@ -16162,8 +16140,8 @@
       <c r="K174" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L174" s="8" t="n">
-        <v>7.5</v>
+      <c r="L174" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M174" s="8" t="n">
         <v>7.5</v>
@@ -16189,7 +16167,7 @@
         <v>8.5</v>
       </c>
       <c r="V174" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W174" s="9" t="n"/>
       <c r="X174" s="8" t="n">
@@ -16214,8 +16192,8 @@
       <c r="AE174" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AF174" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF174" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG174" s="8" t="n">
         <v>7.5</v>
@@ -16224,7 +16202,7 @@
         <v>25</v>
       </c>
       <c r="AI174" s="11" t="n">
-        <v>195.5</v>
+        <v>197</v>
       </c>
     </row>
     <row r="175" ht="19" customHeight="1">
@@ -16328,8 +16306,8 @@
       <c r="K176" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L176" s="8" t="n">
-        <v>7.5</v>
+      <c r="L176" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M176" s="8" t="n">
         <v>7.5</v>
@@ -16361,14 +16339,12 @@
       <c r="X176" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="Y176" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="Y176" s="14" t="n"/>
       <c r="Z176" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA176" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA176" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB176" s="8" t="n">
         <v>7.5</v>
@@ -16385,10 +16361,10 @@
         <v>7.5</v>
       </c>
       <c r="AH176" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI176" s="11" t="n">
-        <v>188</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="177" ht="19" customHeight="1">
@@ -16456,7 +16432,7 @@
         <v>8.5</v>
       </c>
       <c r="V177" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W177" s="9" t="n"/>
       <c r="X177" s="8" t="n">
@@ -16489,7 +16465,7 @@
         <v>25</v>
       </c>
       <c r="AI177" s="11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="178" ht="19" customHeight="1">
@@ -16557,7 +16533,7 @@
         <v>8.5</v>
       </c>
       <c r="V178" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W178" s="9" t="n"/>
       <c r="X178" s="8" t="n">
@@ -16590,7 +16566,7 @@
         <v>25</v>
       </c>
       <c r="AI178" s="11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="179" ht="19" customHeight="1">
@@ -16632,7 +16608,7 @@
         <v>7.5</v>
       </c>
       <c r="N179" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O179" s="7" t="n">
         <v>9.5</v>
@@ -16689,7 +16665,7 @@
         <v>24</v>
       </c>
       <c r="AI179" s="11" t="n">
-        <v>191.5</v>
+        <v>192</v>
       </c>
     </row>
     <row r="180" ht="19" customHeight="1">
@@ -16730,9 +16706,7 @@
       <c r="K180" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="L180" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="L180" s="14" t="n"/>
       <c r="M180" s="8" t="n">
         <v>7.5</v>
       </c>
@@ -16749,7 +16723,7 @@
         <v>7.5</v>
       </c>
       <c r="R180" s="8" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="S180" s="8" t="n">
         <v>7.5</v>
@@ -16795,10 +16769,10 @@
         <v>7.5</v>
       </c>
       <c r="AH180" s="10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI180" s="11" t="n">
-        <v>217.5</v>
+        <v>208.9</v>
       </c>
     </row>
     <row r="181" ht="19" customHeight="1">
@@ -16870,7 +16844,7 @@
         <v>10</v>
       </c>
       <c r="Z181" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AA181" s="8" t="n">
         <v>7.5</v>
@@ -16895,7 +16869,7 @@
         <v>23</v>
       </c>
       <c r="AI181" s="11" t="n">
-        <v>184.5</v>
+        <v>185</v>
       </c>
     </row>
     <row r="182" ht="19" customHeight="1">
@@ -16933,7 +16907,7 @@
         <v>7.5</v>
       </c>
       <c r="N182" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O182" s="7" t="n">
         <v>9.5</v>
@@ -16976,7 +16950,7 @@
       </c>
       <c r="AD182" s="9" t="n"/>
       <c r="AE182" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF182" s="7" t="n">
         <v>8</v>
@@ -16988,7 +16962,7 @@
         <v>21</v>
       </c>
       <c r="AI182" s="11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="183" ht="19" customHeight="1">
@@ -17033,17 +17007,15 @@
       <c r="M183" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="N183" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="N183" s="6" t="n"/>
       <c r="O183" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="P183" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q183" s="8" t="n">
-        <v>7.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="Q183" s="7" t="n">
+        <v>14.5</v>
       </c>
       <c r="R183" s="8" t="n">
         <v>7.5</v>
@@ -17088,7 +17060,7 @@
       </c>
       <c r="AG183" s="6" t="n"/>
       <c r="AH183" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI183" s="11" t="n">
         <v>191.5</v>
@@ -17166,7 +17138,7 @@
       <c r="W184" s="9" t="n"/>
       <c r="X184" s="14" t="n"/>
       <c r="Y184" s="7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z184" s="8" t="n">
         <v>7.5</v>
@@ -17196,7 +17168,7 @@
         <v>27</v>
       </c>
       <c r="AI184" s="11" t="n">
-        <v>260</v>
+        <v>260.5</v>
       </c>
     </row>
     <row r="185" ht="19" customHeight="1">
@@ -17219,8 +17191,8 @@
       <c r="E185" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F185" s="8" t="n">
-        <v>7.5</v>
+      <c r="F185" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G185" s="7" t="n">
         <v>8</v>
@@ -17230,7 +17202,7 @@
       </c>
       <c r="I185" s="9" t="n"/>
       <c r="J185" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="K185" s="7" t="n">
         <v>8.5</v>
@@ -17247,7 +17219,7 @@
       </c>
       <c r="P185" s="9" t="n"/>
       <c r="Q185" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R185" s="6" t="n"/>
       <c r="S185" s="8" t="n">
@@ -17260,7 +17232,7 @@
         <v>8.5</v>
       </c>
       <c r="V185" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W185" s="7" t="n">
         <v>10</v>
@@ -17274,11 +17246,11 @@
       <c r="Z185" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA185" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AB185" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA185" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB185" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC185" s="8" t="n">
         <v>7.5</v>
@@ -17297,7 +17269,7 @@
         <v>25</v>
       </c>
       <c r="AI185" s="11" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="186" ht="19" customHeight="1">
@@ -17321,7 +17293,7 @@
       <c r="H186" s="14" t="n"/>
       <c r="I186" s="9" t="n"/>
       <c r="J186" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="K186" s="7" t="n">
         <v>8.5</v>
@@ -17352,7 +17324,7 @@
         <v>2</v>
       </c>
       <c r="AI186" s="11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" ht="19" customHeight="1">
@@ -17391,8 +17363,8 @@
       <c r="K187" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L187" s="8" t="n">
-        <v>7.5</v>
+      <c r="L187" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M187" s="8" t="n">
         <v>7.5</v>
@@ -17416,7 +17388,7 @@
         <v>8.5</v>
       </c>
       <c r="V187" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W187" s="9" t="n"/>
       <c r="X187" s="8" t="n">
@@ -17428,30 +17400,28 @@
       <c r="Z187" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA187" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AB187" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="AA187" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB187" s="6" t="n"/>
       <c r="AC187" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AD187" s="9" t="n"/>
       <c r="AE187" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF187" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF187" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG187" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AH187" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI187" s="11" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="188" ht="19" customHeight="1">
@@ -17484,9 +17454,7 @@
         <v>7.5</v>
       </c>
       <c r="I188" s="9" t="n"/>
-      <c r="J188" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="J188" s="14" t="n"/>
       <c r="K188" s="8" t="n">
         <v>7.5</v>
       </c>
@@ -17536,17 +17504,15 @@
       <c r="AE188" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AF188" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="AF188" s="14" t="n"/>
       <c r="AG188" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AH188" s="10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI188" s="11" t="n">
-        <v>168</v>
+        <v>153</v>
       </c>
     </row>
     <row r="189" ht="19" customHeight="1">
@@ -17672,8 +17638,8 @@
           <t>ŞÖFÖR</t>
         </is>
       </c>
-      <c r="D190" s="8" t="n">
-        <v>7.5</v>
+      <c r="D190" s="7" t="n">
+        <v>14.5</v>
       </c>
       <c r="E190" s="8" t="n">
         <v>7</v>
@@ -17682,9 +17648,7 @@
         <v>8</v>
       </c>
       <c r="G190" s="14" t="n"/>
-      <c r="H190" s="8" t="n">
-        <v>7</v>
-      </c>
+      <c r="H190" s="14" t="n"/>
       <c r="I190" s="8" t="n">
         <v>7</v>
       </c>
@@ -17703,14 +17667,12 @@
       <c r="N190" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="O190" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P190" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Q190" s="8" t="n">
-        <v>7.5</v>
+      <c r="O190" s="7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="P190" s="9" t="n"/>
+      <c r="Q190" s="7" t="n">
+        <v>14.56</v>
       </c>
       <c r="R190" s="8" t="n">
         <v>7.5</v>
@@ -17723,17 +17685,15 @@
         <v>8</v>
       </c>
       <c r="V190" s="14" t="n"/>
-      <c r="W190" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="X190" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y190" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z190" s="8" t="n">
-        <v>7.5</v>
+      <c r="W190" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="X190" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y190" s="14" t="n"/>
+      <c r="Z190" s="7" t="n">
+        <v>15.53</v>
       </c>
       <c r="AA190" s="8" t="n">
         <v>7.5</v>
@@ -17753,10 +17713,10 @@
       </c>
       <c r="AG190" s="14" t="n"/>
       <c r="AH190" s="10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI190" s="11" t="n">
-        <v>187.5</v>
+        <v>195.09</v>
       </c>
     </row>
     <row r="191" ht="19" customHeight="1">
@@ -17779,23 +17739,23 @@
       <c r="K191" s="6" t="n"/>
       <c r="L191" s="6" t="n"/>
       <c r="M191" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N191" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O191" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P191" s="9" t="n"/>
       <c r="Q191" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R191" s="8" t="n">
         <v>4</v>
       </c>
       <c r="S191" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T191" s="6" t="n"/>
       <c r="U191" s="6" t="n"/>
@@ -17815,7 +17775,7 @@
         <v>6</v>
       </c>
       <c r="AI191" s="11" t="n">
-        <v>61.5</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="192" ht="19" customHeight="1">
@@ -17838,8 +17798,8 @@
       <c r="E192" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F192" s="8" t="n">
-        <v>7.5</v>
+      <c r="F192" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>8</v>
@@ -17884,8 +17844,8 @@
       <c r="AA192" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB192" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB192" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC192" s="8" t="n">
         <v>7.5</v>
@@ -17904,7 +17864,7 @@
         <v>19</v>
       </c>
       <c r="AI192" s="11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="193" ht="19" customHeight="1">
@@ -18045,7 +18005,7 @@
         <v>7.5</v>
       </c>
       <c r="Z194" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AA194" s="8" t="n">
         <v>7.5</v>
@@ -18066,7 +18026,7 @@
         <v>17</v>
       </c>
       <c r="AI194" s="11" t="n">
-        <v>130.5</v>
+        <v>131</v>
       </c>
     </row>
     <row r="195" ht="19" customHeight="1">
@@ -18103,7 +18063,7 @@
         <v>7.5</v>
       </c>
       <c r="K195" s="8" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L195" s="8" t="n">
         <v>7.5</v>
@@ -18137,11 +18097,9 @@
       <c r="W195" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="X195" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Y195" s="8" t="n">
-        <v>7.5</v>
+      <c r="X195" s="6" t="n"/>
+      <c r="Y195" s="7" t="n">
+        <v>14.45</v>
       </c>
       <c r="Z195" s="8" t="n">
         <v>7.5</v>
@@ -18164,10 +18122,10 @@
       </c>
       <c r="AG195" s="6" t="n"/>
       <c r="AH195" s="10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI195" s="11" t="n">
-        <v>187</v>
+        <v>186.95</v>
       </c>
     </row>
     <row r="196" ht="19" customHeight="1">
@@ -18217,8 +18175,8 @@
         <v>10.5</v>
       </c>
       <c r="P196" s="9" t="n"/>
-      <c r="Q196" s="7" t="n">
-        <v>10.5</v>
+      <c r="Q196" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="R196" s="7" t="n">
         <v>10.5</v>
@@ -18260,7 +18218,7 @@
         <v>21</v>
       </c>
       <c r="AI196" s="11" t="n">
-        <v>194</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="197" ht="19" customHeight="1">
@@ -18285,7 +18243,7 @@
       <c r="I197" s="9" t="n"/>
       <c r="J197" s="6" t="n"/>
       <c r="K197" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L197" s="6" t="n"/>
       <c r="M197" s="6" t="n"/>
@@ -18297,17 +18255,17 @@
       <c r="S197" s="6" t="n"/>
       <c r="T197" s="6" t="n"/>
       <c r="U197" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="V197" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W197" s="9" t="n"/>
       <c r="X197" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y197" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z197" s="6" t="n"/>
       <c r="AA197" s="6" t="n"/>
@@ -18315,17 +18273,17 @@
       <c r="AC197" s="6" t="n"/>
       <c r="AD197" s="9" t="n"/>
       <c r="AE197" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF197" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG197" s="6" t="n"/>
       <c r="AH197" s="10" t="n">
         <v>7</v>
       </c>
       <c r="AI197" s="11" t="n">
-        <v>80.5</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="198" ht="19" customHeight="1">
@@ -18384,7 +18342,7 @@
         <v>9.5</v>
       </c>
       <c r="S198" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="T198" s="14" t="n"/>
       <c r="U198" s="7" t="n">
@@ -18424,7 +18382,7 @@
         <v>24</v>
       </c>
       <c r="AI198" s="11" t="n">
-        <v>192.5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" ht="19" customHeight="1">
@@ -18453,8 +18411,8 @@
       <c r="G199" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="H199" s="8" t="n">
-        <v>7.5</v>
+      <c r="H199" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="I199" s="9" t="n"/>
       <c r="J199" s="8" t="n">
@@ -18519,7 +18477,7 @@
         <v>22</v>
       </c>
       <c r="AI199" s="11" t="n">
-        <v>178</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="200" ht="19" customHeight="1">
@@ -18547,49 +18505,49 @@
       </c>
       <c r="I200" s="9" t="n"/>
       <c r="J200" s="7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="K200" s="14" t="n"/>
       <c r="L200" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M200" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N200" s="7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="O200" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P200" s="9" t="n"/>
-      <c r="Q200" s="7" t="n">
-        <v>10.5</v>
+      <c r="Q200" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="R200" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="S200" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T200" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U200" s="14" t="n"/>
       <c r="V200" s="14" t="n"/>
       <c r="W200" s="9" t="n"/>
       <c r="X200" s="14" t="n"/>
-      <c r="Y200" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z200" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA200" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AB200" s="7" t="n">
-        <v>10.5</v>
+      <c r="Y200" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z200" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA200" s="7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AB200" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="AC200" s="14" t="n"/>
       <c r="AD200" s="9" t="n"/>
@@ -18600,7 +18558,7 @@
         <v>15</v>
       </c>
       <c r="AI200" s="11" t="n">
-        <v>150.5</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="201" ht="19" customHeight="1">
@@ -18724,8 +18682,8 @@
       <c r="K202" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L202" s="8" t="n">
-        <v>7.5</v>
+      <c r="L202" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M202" s="14" t="n"/>
       <c r="N202" s="14" t="n"/>
@@ -18747,7 +18705,7 @@
         <v>8.5</v>
       </c>
       <c r="V202" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W202" s="9" t="n"/>
       <c r="X202" s="8" t="n">
@@ -18759,8 +18717,8 @@
       <c r="Z202" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA202" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA202" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB202" s="8" t="n">
         <v>7.5</v>
@@ -18772,8 +18730,8 @@
       <c r="AE202" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AF202" s="8" t="n">
-        <v>7.5</v>
+      <c r="AF202" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG202" s="8" t="n">
         <v>7.5</v>
@@ -18782,7 +18740,7 @@
         <v>23</v>
       </c>
       <c r="AI202" s="11" t="n">
-        <v>179.5</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="203" ht="19" customHeight="1">
@@ -18824,7 +18782,7 @@
         <v>9.5</v>
       </c>
       <c r="L203" s="7" t="n">
-        <v>9.5</v>
+        <v>8.68</v>
       </c>
       <c r="M203" s="7" t="n">
         <v>11</v>
@@ -18832,8 +18790,8 @@
       <c r="N203" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="O203" s="8" t="n">
-        <v>0.5</v>
+      <c r="O203" s="7" t="n">
+        <v>12</v>
       </c>
       <c r="P203" s="8" t="n">
         <v>7.5</v>
@@ -18863,7 +18821,7 @@
         <v>10.5</v>
       </c>
       <c r="Y203" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z203" s="7" t="n">
         <v>11</v>
@@ -18891,7 +18849,7 @@
         <v>29</v>
       </c>
       <c r="AI203" s="11" t="n">
-        <v>250.5</v>
+        <v>261.68</v>
       </c>
     </row>
     <row r="204" ht="19" customHeight="1">
@@ -18921,7 +18879,7 @@
       <c r="L204" s="14" t="n"/>
       <c r="M204" s="14" t="n"/>
       <c r="N204" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O204" s="7" t="n">
         <v>9</v>
@@ -18950,10 +18908,10 @@
         <v>9</v>
       </c>
       <c r="AA204" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB204" s="8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AC204" s="8" t="n">
         <v>7</v>
@@ -18970,7 +18928,7 @@
         <v>16</v>
       </c>
       <c r="AI204" s="11" t="n">
-        <v>126</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="205" ht="19" customHeight="1">
@@ -19002,45 +18960,45 @@
       <c r="H205" s="6" t="n"/>
       <c r="I205" s="9" t="n"/>
       <c r="J205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="K205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P205" s="9" t="n"/>
       <c r="Q205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R205" s="8" t="n">
         <v>4</v>
       </c>
       <c r="S205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="V205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W205" s="9" t="n"/>
       <c r="X205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y205" s="8" t="n">
         <v>2</v>
@@ -19049,21 +19007,21 @@
       <c r="AA205" s="6" t="n"/>
       <c r="AB205" s="6" t="n"/>
       <c r="AC205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD205" s="9" t="n"/>
       <c r="AE205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF205" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG205" s="6" t="n"/>
       <c r="AH205" s="10" t="n">
         <v>21</v>
       </c>
       <c r="AI205" s="11" t="n">
-        <v>208.5</v>
+        <v>193.5</v>
       </c>
     </row>
     <row r="206" ht="19" customHeight="1">
@@ -19133,7 +19091,7 @@
         <v>8.5</v>
       </c>
       <c r="V206" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W206" s="9" t="n"/>
       <c r="X206" s="8" t="n">
@@ -19166,7 +19124,7 @@
         <v>26</v>
       </c>
       <c r="AI206" s="11" t="n">
-        <v>202.5</v>
+        <v>201.5</v>
       </c>
     </row>
     <row r="207" ht="19" customHeight="1">
@@ -19246,8 +19204,8 @@
       <c r="Z207" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA207" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA207" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB207" s="8" t="n">
         <v>7.5</v>
@@ -19257,10 +19215,10 @@
       </c>
       <c r="AD207" s="9" t="n"/>
       <c r="AE207" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF207" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF207" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG207" s="8" t="n">
         <v>7.5</v>
@@ -19269,7 +19227,7 @@
         <v>26</v>
       </c>
       <c r="AI207" s="11" t="n">
-        <v>204</v>
+        <v>205.5</v>
       </c>
     </row>
     <row r="208" ht="19" customHeight="1">
@@ -19388,7 +19346,7 @@
         <v>7.5</v>
       </c>
       <c r="N209" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O209" s="7" t="n">
         <v>9.5</v>
@@ -19419,7 +19377,7 @@
         <v>7</v>
       </c>
       <c r="AI209" s="11" t="n">
-        <v>56.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="210" ht="19" customHeight="1">
@@ -19538,9 +19496,7 @@
       <c r="N211" s="7" t="n">
         <v>10.5</v>
       </c>
-      <c r="O211" s="7" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="O211" s="6" t="n"/>
       <c r="P211" s="9" t="n"/>
       <c r="Q211" s="6" t="n"/>
       <c r="R211" s="6" t="n"/>
@@ -19566,10 +19522,10 @@
       <c r="AF211" s="6" t="n"/>
       <c r="AG211" s="6" t="n"/>
       <c r="AH211" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI211" s="11" t="n">
-        <v>109.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="212" ht="19" customHeight="1">
@@ -19600,19 +19556,19 @@
       <c r="I212" s="9" t="n"/>
       <c r="J212" s="14" t="n"/>
       <c r="K212" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L212" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M212" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N212" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O212" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="P212" s="9" t="n"/>
       <c r="Q212" s="14" t="n"/>
@@ -19662,7 +19618,7 @@
         <v>23</v>
       </c>
       <c r="AI212" s="11" t="n">
-        <v>231.5</v>
+        <v>226.5</v>
       </c>
     </row>
     <row r="213" ht="19" customHeight="1">
@@ -19685,8 +19641,8 @@
       <c r="E213" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F213" s="8" t="n">
-        <v>7.5</v>
+      <c r="F213" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G213" s="7" t="n">
         <v>8</v>
@@ -19706,7 +19662,7 @@
         <v>7.5</v>
       </c>
       <c r="N213" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O213" s="7" t="n">
         <v>9.5</v>
@@ -19739,7 +19695,7 @@
         <v>13</v>
       </c>
       <c r="AI213" s="11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="214" ht="19" customHeight="1">
@@ -19762,8 +19718,8 @@
       <c r="E214" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F214" s="8" t="n">
-        <v>7.5</v>
+      <c r="F214" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G214" s="7" t="n">
         <v>8</v>
@@ -19838,7 +19794,7 @@
         <v>24</v>
       </c>
       <c r="AI214" s="11" t="n">
-        <v>192.5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="215" ht="19" customHeight="1">
@@ -19923,7 +19879,7 @@
         <v>10.5</v>
       </c>
       <c r="AE215" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF215" s="8" t="n">
         <v>7.5</v>
@@ -19933,7 +19889,7 @@
         <v>22</v>
       </c>
       <c r="AI215" s="11" t="n">
-        <v>178.5</v>
+        <v>179</v>
       </c>
     </row>
     <row r="216" ht="19" customHeight="1">
@@ -19953,8 +19909,8 @@
       <c r="D216" s="14" t="n"/>
       <c r="E216" s="14" t="n"/>
       <c r="F216" s="14" t="n"/>
-      <c r="G216" s="8" t="n">
-        <v>7.5</v>
+      <c r="G216" s="7" t="n">
+        <v>10.5</v>
       </c>
       <c r="H216" s="8" t="n">
         <v>7.5</v>
@@ -19971,14 +19927,14 @@
       </c>
       <c r="M216" s="14" t="n"/>
       <c r="N216" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O216" s="7" t="n">
         <v>9</v>
       </c>
       <c r="P216" s="9" t="n"/>
       <c r="Q216" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R216" s="7" t="n">
         <v>8</v>
@@ -20006,10 +19962,10 @@
         <v>9</v>
       </c>
       <c r="AA216" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB216" s="8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AC216" s="8" t="n">
         <v>7</v>
@@ -20026,7 +19982,7 @@
         <v>21</v>
       </c>
       <c r="AI216" s="11" t="n">
-        <v>158.5</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="217" ht="19" customHeight="1">
@@ -20056,8 +20012,8 @@
         <v>7.5</v>
       </c>
       <c r="H217" s="6" t="n"/>
-      <c r="I217" s="8" t="n">
-        <v>7.5</v>
+      <c r="I217" s="7" t="n">
+        <v>14.5</v>
       </c>
       <c r="J217" s="8" t="n">
         <v>7.5</v>
@@ -20096,7 +20052,7 @@
         <v>8.5</v>
       </c>
       <c r="V217" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W217" s="9" t="n"/>
       <c r="X217" s="8" t="n">
@@ -20129,7 +20085,7 @@
         <v>26</v>
       </c>
       <c r="AI217" s="11" t="n">
-        <v>202.5</v>
+        <v>208.5</v>
       </c>
     </row>
     <row r="218" ht="19" customHeight="1">
@@ -20155,11 +20111,11 @@
       <c r="J218" s="14" t="n"/>
       <c r="K218" s="14" t="n"/>
       <c r="L218" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M218" s="14" t="n"/>
       <c r="N218" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="O218" s="14" t="n"/>
       <c r="P218" s="9" t="n"/>
@@ -20168,10 +20124,10 @@
         <v>4</v>
       </c>
       <c r="S218" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="T218" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="U218" s="14" t="n"/>
       <c r="V218" s="14" t="n"/>
@@ -20190,7 +20146,7 @@
         <v>5</v>
       </c>
       <c r="AI218" s="11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="219" ht="19" customHeight="1">
@@ -20260,7 +20216,7 @@
         <v>8.5</v>
       </c>
       <c r="V219" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W219" s="9" t="n"/>
       <c r="X219" s="8" t="n">
@@ -20293,7 +20249,7 @@
         <v>26</v>
       </c>
       <c r="AI219" s="11" t="n">
-        <v>202.5</v>
+        <v>201.5</v>
       </c>
     </row>
     <row r="220" ht="19" customHeight="1">
@@ -20316,8 +20272,8 @@
       <c r="E220" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F220" s="8" t="n">
-        <v>7.5</v>
+      <c r="F220" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G220" s="8" t="n">
         <v>7.5</v>
@@ -20352,7 +20308,7 @@
         <v>4</v>
       </c>
       <c r="AI220" s="11" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="221" ht="19" customHeight="1">
@@ -20430,8 +20386,8 @@
       <c r="E222" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F222" s="8" t="n">
-        <v>7.5</v>
+      <c r="F222" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G222" s="7" t="n">
         <v>8</v>
@@ -20447,7 +20403,7 @@
         <v>7.5</v>
       </c>
       <c r="N222" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O222" s="7" t="n">
         <v>9.5</v>
@@ -20482,8 +20438,8 @@
       <c r="AA222" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB222" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB222" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC222" s="8" t="n">
         <v>7.5</v>
@@ -20502,7 +20458,7 @@
         <v>22</v>
       </c>
       <c r="AI222" s="11" t="n">
-        <v>175.5</v>
+        <v>177</v>
       </c>
     </row>
     <row r="223" ht="19" customHeight="1">
@@ -20583,8 +20539,8 @@
       <c r="F224" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="G224" s="8" t="n">
-        <v>1</v>
+      <c r="G224" s="7" t="n">
+        <v>18</v>
       </c>
       <c r="H224" s="14" t="n"/>
       <c r="I224" s="9" t="n"/>
@@ -20656,7 +20612,7 @@
         <v>24</v>
       </c>
       <c r="AI224" s="11" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="225" ht="19" customHeight="1">
@@ -20718,7 +20674,7 @@
       <c r="T225" s="6" t="n"/>
       <c r="U225" s="6" t="n"/>
       <c r="V225" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W225" s="9" t="n"/>
       <c r="X225" s="8" t="n">
@@ -20753,7 +20709,7 @@
         <v>23</v>
       </c>
       <c r="AI225" s="11" t="n">
-        <v>181.5</v>
+        <v>182</v>
       </c>
     </row>
     <row r="226" ht="19" customHeight="1">
@@ -20782,8 +20738,8 @@
       <c r="G226" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="H226" s="8" t="n">
-        <v>7.5</v>
+      <c r="H226" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="I226" s="9" t="n"/>
       <c r="J226" s="8" t="n">
@@ -20816,7 +20772,7 @@
         <v>6.5</v>
       </c>
       <c r="U226" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="V226" s="7" t="n">
         <v>9.5</v>
@@ -20854,7 +20810,7 @@
         <v>25</v>
       </c>
       <c r="AI226" s="11" t="n">
-        <v>196.5</v>
+        <v>197.5</v>
       </c>
     </row>
     <row r="227" ht="19" customHeight="1">
@@ -20879,27 +20835,27 @@
       </c>
       <c r="H227" s="6" t="n"/>
       <c r="I227" s="9" t="n"/>
-      <c r="J227" s="7" t="n">
-        <v>10.5</v>
+      <c r="J227" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="K227" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L227" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M227" s="7" t="n">
-        <v>10.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="M227" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="N227" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="O227" s="7" t="n">
-        <v>10.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="O227" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="P227" s="9" t="n"/>
       <c r="Q227" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R227" s="6" t="n"/>
       <c r="S227" s="6" t="n"/>
@@ -20908,30 +20864,30 @@
         <v>7.5</v>
       </c>
       <c r="V227" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="W227" s="9" t="n"/>
       <c r="X227" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="Y227" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z227" s="7" t="n">
-        <v>10</v>
+      <c r="Y227" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z227" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="AA227" s="6" t="n"/>
       <c r="AB227" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC227" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD227" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE227" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AF227" s="6" t="n"/>
       <c r="AG227" s="6" t="n"/>
@@ -20939,7 +20895,7 @@
         <v>17</v>
       </c>
       <c r="AI227" s="11" t="n">
-        <v>177.5</v>
+        <v>154.5</v>
       </c>
     </row>
     <row r="228" ht="19" customHeight="1">
@@ -20966,8 +20922,8 @@
       <c r="I228" s="9" t="n"/>
       <c r="J228" s="14" t="n"/>
       <c r="K228" s="14" t="n"/>
-      <c r="L228" s="8" t="n">
-        <v>7.5</v>
+      <c r="L228" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M228" s="8" t="n">
         <v>7.5</v>
@@ -20998,17 +20954,15 @@
         <v>8.5</v>
       </c>
       <c r="W228" s="9" t="n"/>
-      <c r="X228" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="X228" s="14" t="n"/>
       <c r="Y228" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="Z228" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA228" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA228" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB228" s="8" t="n">
         <v>7.5</v>
@@ -21027,10 +20981,10 @@
         <v>7.5</v>
       </c>
       <c r="AH228" s="10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI228" s="11" t="n">
-        <v>156.5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="229" ht="19" customHeight="1">
@@ -21053,11 +21007,11 @@
       <c r="K229" s="6" t="n"/>
       <c r="L229" s="6" t="n"/>
       <c r="M229" s="6" t="n"/>
-      <c r="N229" s="8" t="n">
-        <v>7.5</v>
+      <c r="N229" s="7" t="n">
+        <v>10.5</v>
       </c>
       <c r="O229" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="P229" s="9" t="n"/>
       <c r="Q229" s="6" t="n"/>
@@ -21072,7 +21026,7 @@
         <v>8.5</v>
       </c>
       <c r="V229" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W229" s="9" t="n"/>
       <c r="X229" s="7" t="n">
@@ -21105,7 +21059,7 @@
         <v>14</v>
       </c>
       <c r="AI229" s="11" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="230" ht="19" customHeight="1">
@@ -21160,7 +21114,7 @@
         <v>8.5</v>
       </c>
       <c r="Q230" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="R230" s="14" t="n"/>
       <c r="S230" s="14" t="n"/>
@@ -21177,11 +21131,9 @@
       <c r="X230" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="Y230" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z230" s="8" t="n">
-        <v>7.5</v>
+      <c r="Y230" s="14" t="n"/>
+      <c r="Z230" s="7" t="n">
+        <v>15.5</v>
       </c>
       <c r="AA230" s="8" t="n">
         <v>7.5</v>
@@ -21192,21 +21144,21 @@
       <c r="AC230" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AD230" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AE230" s="8" t="n">
-        <v>7.5</v>
+      <c r="AD230" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE230" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AF230" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="AG230" s="14" t="n"/>
       <c r="AH230" s="10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI230" s="11" t="n">
-        <v>201.5</v>
+        <v>203.5</v>
       </c>
     </row>
     <row r="231" ht="19" customHeight="1">
@@ -21308,8 +21260,8 @@
       <c r="E232" s="7" t="n">
         <v>9.5</v>
       </c>
-      <c r="F232" s="8" t="n">
-        <v>7.5</v>
+      <c r="F232" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G232" s="7" t="n">
         <v>9.5</v>
@@ -21338,7 +21290,7 @@
       </c>
       <c r="P232" s="9" t="n"/>
       <c r="Q232" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R232" s="7" t="n">
         <v>10.5</v>
@@ -21356,8 +21308,8 @@
         <v>7.5</v>
       </c>
       <c r="W232" s="9" t="n"/>
-      <c r="X232" s="8" t="n">
-        <v>7.5</v>
+      <c r="X232" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="Y232" s="8" t="n">
         <v>7.5</v>
@@ -21368,8 +21320,8 @@
       <c r="AA232" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="AB232" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB232" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC232" s="7" t="n">
         <v>10.5</v>
@@ -21386,7 +21338,7 @@
         <v>25</v>
       </c>
       <c r="AI232" s="11" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="233" ht="19" customHeight="1">
@@ -21425,14 +21377,14 @@
       <c r="K233" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L233" s="8" t="n">
-        <v>7.5</v>
+      <c r="L233" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M233" s="8" t="n">
         <v>7.5</v>
       </c>
       <c r="N233" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O233" s="7" t="n">
         <v>9.5</v>
@@ -21477,7 +21429,7 @@
       </c>
       <c r="AD233" s="9" t="n"/>
       <c r="AE233" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF233" s="8" t="n">
         <v>7.5</v>
@@ -21489,7 +21441,7 @@
         <v>26</v>
       </c>
       <c r="AI233" s="11" t="n">
-        <v>205.5</v>
+        <v>207</v>
       </c>
     </row>
     <row r="234" ht="19" customHeight="1">
@@ -21526,7 +21478,7 @@
         <v>7.5</v>
       </c>
       <c r="K234" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L234" s="7" t="n">
         <v>9.5</v>
@@ -21540,7 +21492,7 @@
       <c r="O234" s="14" t="n"/>
       <c r="P234" s="9" t="n"/>
       <c r="Q234" s="7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R234" s="7" t="n">
         <v>9.5</v>
@@ -21552,7 +21504,7 @@
         <v>8.5</v>
       </c>
       <c r="U234" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="V234" s="7" t="n">
         <v>10.5</v>
@@ -21565,7 +21517,7 @@
         <v>8.5</v>
       </c>
       <c r="Z234" s="7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AA234" s="7" t="n">
         <v>8.5</v>
@@ -21590,7 +21542,7 @@
         <v>25</v>
       </c>
       <c r="AI234" s="11" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="235" ht="19" customHeight="1">
@@ -21749,10 +21701,10 @@
         <v>9</v>
       </c>
       <c r="R236" s="8" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="S236" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="T236" s="14" t="n"/>
       <c r="U236" s="14" t="n"/>
@@ -21772,7 +21724,7 @@
         <v>16</v>
       </c>
       <c r="AI236" s="11" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="237" ht="19" customHeight="1">
@@ -21795,8 +21747,8 @@
       <c r="E237" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="F237" s="8" t="n">
-        <v>7.5</v>
+      <c r="F237" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="G237" s="7" t="n">
         <v>8</v>
@@ -21849,8 +21801,8 @@
       <c r="AA237" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB237" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB237" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC237" s="6" t="n"/>
       <c r="AD237" s="9" t="n"/>
@@ -21861,7 +21813,7 @@
         <v>19</v>
       </c>
       <c r="AI237" s="11" t="n">
-        <v>152.5</v>
+        <v>153.5</v>
       </c>
     </row>
     <row r="238" ht="19" customHeight="1">
@@ -21939,7 +21891,7 @@
         <v>10</v>
       </c>
       <c r="Z238" s="7" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AA238" s="8" t="n">
         <v>7.5</v>
@@ -21964,7 +21916,7 @@
         <v>26</v>
       </c>
       <c r="AI238" s="11" t="n">
-        <v>207.5</v>
+        <v>208</v>
       </c>
     </row>
     <row r="239" ht="19" customHeight="1">
@@ -21998,7 +21950,7 @@
       </c>
       <c r="I239" s="9" t="n"/>
       <c r="J239" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="K239" s="7" t="n">
         <v>8.5</v>
@@ -22014,9 +21966,7 @@
         <v>9.5</v>
       </c>
       <c r="P239" s="9" t="n"/>
-      <c r="Q239" s="7" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="Q239" s="6" t="n"/>
       <c r="R239" s="6" t="n"/>
       <c r="S239" s="8" t="n">
         <v>7.5</v>
@@ -22028,7 +21978,7 @@
         <v>8.5</v>
       </c>
       <c r="V239" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W239" s="7" t="n">
         <v>10</v>
@@ -22042,8 +21992,8 @@
       <c r="Z239" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA239" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA239" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB239" s="6" t="n"/>
       <c r="AC239" s="8" t="n">
@@ -22060,10 +22010,10 @@
         <v>7.5</v>
       </c>
       <c r="AH239" s="10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI239" s="11" t="n">
-        <v>211.5</v>
+        <v>190.5</v>
       </c>
     </row>
     <row r="240" ht="19" customHeight="1">
@@ -22370,9 +22320,7 @@
         <v>7.5</v>
       </c>
       <c r="I244" s="9" t="n"/>
-      <c r="J244" s="8" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="J244" s="14" t="n"/>
       <c r="K244" s="7" t="n">
         <v>8.5</v>
       </c>
@@ -22428,7 +22376,7 @@
       </c>
       <c r="AD244" s="9" t="n"/>
       <c r="AE244" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF244" s="7" t="n">
         <v>8</v>
@@ -22437,10 +22385,10 @@
         <v>7.5</v>
       </c>
       <c r="AH244" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI244" s="11" t="n">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="245" ht="19" customHeight="1">
@@ -22520,8 +22468,8 @@
       <c r="Z245" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA245" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA245" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB245" s="8" t="n">
         <v>7.5</v>
@@ -22531,10 +22479,10 @@
       </c>
       <c r="AD245" s="9" t="n"/>
       <c r="AE245" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF245" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF245" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG245" s="8" t="n">
         <v>7.5</v>
@@ -22543,7 +22491,7 @@
         <v>26</v>
       </c>
       <c r="AI245" s="11" t="n">
-        <v>205</v>
+        <v>206.5</v>
       </c>
     </row>
     <row r="246" ht="19" customHeight="1">
@@ -22587,7 +22535,7 @@
         <v>7.5</v>
       </c>
       <c r="N246" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O246" s="7" t="n">
         <v>9.5</v>
@@ -22624,8 +22572,8 @@
       <c r="AA246" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB246" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB246" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC246" s="8" t="n">
         <v>7.5</v>
@@ -22644,7 +22592,7 @@
         <v>25</v>
       </c>
       <c r="AI246" s="11" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="247" ht="19" customHeight="1">
@@ -22727,8 +22675,8 @@
       <c r="AA247" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB247" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB247" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC247" s="8" t="n">
         <v>7.5</v>
@@ -22747,7 +22695,7 @@
         <v>26</v>
       </c>
       <c r="AI247" s="11" t="n">
-        <v>207.5</v>
+        <v>208</v>
       </c>
     </row>
     <row r="248" ht="19" customHeight="1">
@@ -22838,7 +22786,7 @@
       </c>
       <c r="AD248" s="9" t="n"/>
       <c r="AE248" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AF248" s="14" t="n"/>
       <c r="AG248" s="8" t="n">
@@ -22848,7 +22796,7 @@
         <v>25</v>
       </c>
       <c r="AI248" s="11" t="n">
-        <v>198</v>
+        <v>198.5</v>
       </c>
     </row>
     <row r="249" ht="19" customHeight="1">
@@ -22879,16 +22827,16 @@
       <c r="O249" s="6" t="n"/>
       <c r="P249" s="9" t="n"/>
       <c r="Q249" s="7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="R249" s="8" t="n">
         <v>4</v>
       </c>
       <c r="S249" s="7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="T249" s="7" t="n">
-        <v>10.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="T249" s="8" t="n">
+        <v>7.5</v>
       </c>
       <c r="U249" s="6" t="n"/>
       <c r="V249" s="6" t="n"/>
@@ -22907,7 +22855,7 @@
         <v>4</v>
       </c>
       <c r="AI249" s="11" t="n">
-        <v>37.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="250" ht="19" customHeight="1">
@@ -22951,7 +22899,7 @@
         <v>7.5</v>
       </c>
       <c r="N250" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O250" s="7" t="n">
         <v>9.5</v>
@@ -22975,7 +22923,7 @@
         <v>8.5</v>
       </c>
       <c r="V250" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W250" s="9" t="n"/>
       <c r="X250" s="8" t="n">
@@ -22987,8 +22935,8 @@
       <c r="Z250" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA250" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA250" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB250" s="7" t="n">
         <v>10.5</v>
@@ -23012,7 +22960,7 @@
         <v>27</v>
       </c>
       <c r="AI250" s="11" t="n">
-        <v>217.5</v>
+        <v>219</v>
       </c>
     </row>
     <row r="251" ht="19" customHeight="1">
@@ -23071,10 +23019,10 @@
       </c>
       <c r="AD251" s="9" t="n"/>
       <c r="AE251" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF251" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF251" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG251" s="8" t="n">
         <v>7.5</v>
@@ -23083,7 +23031,7 @@
         <v>10</v>
       </c>
       <c r="AI251" s="11" t="n">
-        <v>78.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="252" ht="19" customHeight="1">
@@ -23125,7 +23073,7 @@
         <v>7.5</v>
       </c>
       <c r="N252" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O252" s="14" t="n"/>
       <c r="P252" s="9" t="n"/>
@@ -23158,8 +23106,8 @@
       <c r="AA252" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB252" s="8" t="n">
-        <v>7.5</v>
+      <c r="AB252" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AC252" s="8" t="n">
         <v>7.5</v>
@@ -23176,7 +23124,7 @@
         <v>21</v>
       </c>
       <c r="AI252" s="11" t="n">
-        <v>165.5</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="253" ht="19" customHeight="1">
@@ -23218,7 +23166,7 @@
         <v>7.5</v>
       </c>
       <c r="N253" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O253" s="7" t="n">
         <v>9.5</v>
@@ -23263,10 +23211,10 @@
       </c>
       <c r="AD253" s="9" t="n"/>
       <c r="AE253" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF253" s="8" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="AF253" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AG253" s="8" t="n">
         <v>7.5</v>
@@ -23275,7 +23223,7 @@
         <v>24</v>
       </c>
       <c r="AI253" s="11" t="n">
-        <v>190</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="254" ht="19" customHeight="1">
@@ -23339,7 +23287,7 @@
         <v>8.5</v>
       </c>
       <c r="V254" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W254" s="9" t="n"/>
       <c r="X254" s="8" t="n">
@@ -23349,8 +23297,8 @@
       <c r="Z254" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="AA254" s="8" t="n">
-        <v>7.5</v>
+      <c r="AA254" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="AB254" s="8" t="n">
         <v>7.5</v>
@@ -23372,7 +23320,7 @@
         <v>23</v>
       </c>
       <c r="AI254" s="11" t="n">
-        <v>181.5</v>
+        <v>182.5</v>
       </c>
     </row>
     <row r="255" ht="19" customHeight="1">
@@ -23409,7 +23357,7 @@
         <v>6</v>
       </c>
       <c r="K255" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L255" s="6" t="n"/>
       <c r="M255" s="6" t="n"/>
@@ -23419,7 +23367,7 @@
       </c>
       <c r="P255" s="9" t="n"/>
       <c r="Q255" s="7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R255" s="7" t="n">
         <v>8</v>
@@ -23447,7 +23395,7 @@
         <v>9</v>
       </c>
       <c r="AA255" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB255" s="8" t="n">
         <v>7</v>
@@ -23467,7 +23415,7 @@
         <v>22</v>
       </c>
       <c r="AI255" s="11" t="n">
-        <v>172</v>
+        <v>173.5</v>
       </c>
     </row>
     <row r="256" ht="19" customHeight="1">
@@ -23506,8 +23454,8 @@
       <c r="K256" s="7" t="n">
         <v>8.5</v>
       </c>
-      <c r="L256" s="8" t="n">
-        <v>7.5</v>
+      <c r="L256" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="M256" s="8" t="n">
         <v>7.5</v>
@@ -23535,7 +23483,7 @@
         <v>8.5</v>
       </c>
       <c r="V256" s="7" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W256" s="9" t="n"/>
       <c r="X256" s="8" t="n">
@@ -23570,7 +23518,7 @@
         <v>26</v>
       </c>
       <c r="AI256" s="11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
